--- a/01_Input/00_CO Validation/Moldova Republic - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Moldova Republic - Energy Projects.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26712"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27018"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ben/Documents/UNDP/Energy/CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="735" documentId="13_ncr:1_{F7DA749C-5740-5D4C-B662-A29A9599CDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EEEF10E-D99F-497F-9CC5-5B7F69FE6ED3}"/>
+  <xr:revisionPtr revIDLastSave="764" documentId="13_ncr:1_{F7DA749C-5740-5D4C-B662-A29A9599CDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2217B78E-2C16-423F-8D84-ABF8487EFE5A}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="740" windowWidth="16100" windowHeight="9660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="740" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId1"/>
-    <sheet name="Projects" sheetId="1" r:id="rId2"/>
-    <sheet name="Beneficiary Categories" sheetId="2" r:id="rId3"/>
+    <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
+    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="129">
   <si>
     <t>Project ID</t>
   </si>
@@ -88,7 +89,7 @@
     <t>https://www.undp.org/moldova/projects/moldova-sustainable-green-cities</t>
   </si>
   <si>
-    <t>Energy (MW added)</t>
+    <t>Electricity Access</t>
   </si>
   <si>
     <t xml:space="preserve">1. Photovoltaic panels for electricity production to cover the costs for interior lightening and lift use for residents of 421 apartments from a multi-storey building;  
@@ -96,7 +97,7 @@
 3. Photovoltaic panels to cover at least 30% of the annual electricity needs of the district Hospital from Singerei </t>
   </si>
   <si>
-    <t>2021-2023</t>
+    <t>421 HH</t>
   </si>
   <si>
     <t xml:space="preserve">Photovoltaic panels were conected to generate energy for  interior lightening and lift use for residents of 421 apartments from a multi-storey building, as well as for the Placement Center for Adults and Older People from Sculeni village, Ungheni district and for the district Hospital from Singerei. 
@@ -116,13 +117,7 @@
     <t>to the CO: Please estimate number of MW or total benefiricaries</t>
   </si>
   <si>
-    <t>Electricity Access</t>
-  </si>
-  <si>
     <t>301 apartments from Chisinau and Balti municipalities</t>
-  </si>
-  <si>
-    <t>2022-2023</t>
   </si>
   <si>
     <t>301 HH</t>
@@ -130,6 +125,9 @@
   <si>
     <t xml:space="preserve">6 multi-storey residential buildings from Chișinău and Bălți municipality (301 apartments) were switched to horizontal system of distribution the thermal energy, that can generate savings up to 30%, and were connected to Domestic Hot Water system 
 After the first heating season, 178 apartments had savings of 90,64 Gcal or about 17% from expected consumption with the vertical system (forecast). The energy saving for preparation of hot water were 23,62%. The total savings in Chisinau based on unused energy are more than US $18 thousand. In Balti, the saving of this year compared to saving from previous years varies from 33.64% to 53.79%. The three multi-story buildings from Balti consumed in 2022-2023 season 270 Gcal less compared with 2021-2022 consumption of these buildings, and with 388 Gcal less compared with 2020-2021 consumption. </t>
+  </si>
+  <si>
+    <t>Energy (MW added)</t>
   </si>
   <si>
     <t>2 solar trees generating green energy to
@@ -161,7 +159,7 @@
     <t>66 electric vehicles charging stations installed</t>
   </si>
   <si>
-    <t>2019-2022</t>
+    <t>2000 HH</t>
   </si>
   <si>
     <t xml:space="preserve">In the Repubic of Moldova are registred about 2000 electric vehicles. </t>
@@ -177,9 +175,6 @@
   </si>
   <si>
     <t>4 editions of the electric cars’ marathon</t>
-  </si>
-  <si>
-    <t>2018-2021</t>
   </si>
   <si>
     <t>Other Energy Services</t>
@@ -188,9 +183,6 @@
     <t>An Energy Management Information System
 (EMIS) and smart meters were installed in 17 public buildings from
 Chisinau</t>
-  </si>
-  <si>
-    <t>2020-2023</t>
   </si>
   <si>
     <t>By 30 June 2023, EMIS system are monitoring the consumption data of 4.5 thousand public buildings from Moldova. The system have consumption data from the last three years. The main energy and water suppliers (Premier Energy, Apa-Canal, Termoelectrica, Cet-Nord, Red-Nord, Apa Canal Floresti) automatically transfer data on energy consumption and other resources to EMIS.</t>
@@ -256,6 +248,9 @@
 3. Energy consumption as a result of implemented energy efficiency and saving measures per target group (HHs, public buildings).</t>
   </si>
   <si>
+    <t>700000 HH</t>
+  </si>
+  <si>
     <t>National Programms on Green home and Vouchers on replacing non efficient home appliances  have been drafted and being piloted during 2023-2024</t>
   </si>
   <si>
@@ -263,11 +258,6 @@
   </si>
   <si>
     <t>Addressing the impacts of the energy crisis in the Republic of Moldova | United Nations Development Programme (undp.org)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023:
-Sweden: 9,826,008 USD
-Switzerland: 6,666,666 USD </t>
   </si>
   <si>
     <t>Support with defining “energy vulnerable consumer” ​
@@ -279,10 +269,13 @@
 Mobilization of additional funds from development partners and aid through the Energy Vulnerability Fund;​</t>
   </si>
   <si>
-    <t>The law on Energy Vulnerability Fund was drafted;
+    <t xml:space="preserve">The law on Energy Vulnerability Fund was drafted;
 The concept and implementation mechanism of the Energy Vulnerability Fund was developed;
 The Energy Vulnerability Information System was developed;
-An information campaign to support registration of beneficiaries on the online platform of the Energy Vulnerability Fund conducted;</t>
+An information campaign to support registration of beneficiaries on the online platform of the Energy Vulnerability Fund conducted;
+2023:
+Sweden: 9,826,008 USD
+Switzerland: 6,666,666 USD </t>
   </si>
   <si>
     <t>Multidimensional response to emerging human security challenges - "Biomass revitalization"</t>
@@ -312,16 +305,13 @@
     <t>Non-VF</t>
   </si>
   <si>
+    <t xml:space="preserve">Emergency support for agri-producers /energy technologies </t>
+  </si>
+  <si>
+    <t>https://www.undp.org/moldova/projects/emergency-support-agri-producers-context-socio-economic-climate-and-energy-crisis</t>
+  </si>
+  <si>
     <t>Medium Enterprises</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emergency support for agri-producers /energy technologies </t>
-  </si>
-  <si>
-    <t>https://www.undp.org/moldova/projects/emergency-support-agri-producers-context-socio-economic-climate-and-energy-crisis</t>
-  </si>
-  <si>
-    <t>US$1,983,621 ($689,308 managed by UNDP)</t>
   </si>
   <si>
     <t>SMEs, vulnerable small farmers (particularly women-led farms and young people) in rural areas</t>
@@ -331,10 +321,43 @@
 </t>
   </si>
   <si>
+    <t>20 micro agri-producers and 10 small and medium agri-producers benefit from the implementation of renewable energy and energy-efficient technologies (biomass boilers in greenhouses, photovoltaic, among others).
+US$1,983,621 ($689,308 managed by UNDP)</t>
+  </si>
+  <si>
+    <t>Austria (ADA) $670,123 (2024)</t>
+  </si>
+  <si>
+    <t>2021-2023</t>
+  </si>
+  <si>
+    <t>2022-2023</t>
+  </si>
+  <si>
+    <t>2019-2022</t>
+  </si>
+  <si>
+    <t>2018-2021</t>
+  </si>
+  <si>
+    <t>2020-2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023:
+Sweden: 9,826,008 USD
+Switzerland: 6,666,666 USD </t>
+  </si>
+  <si>
+    <t>The law on Energy Vulnerability Fund was drafted;
+The concept and implementation mechanism of the Energy Vulnerability Fund was developed;
+The Energy Vulnerability Information System was developed;
+An information campaign to support registration of beneficiaries on the online platform of the Energy Vulnerability Fund conducted;</t>
+  </si>
+  <si>
+    <t>US$1,983,621 ($689,308 managed by UNDP)</t>
+  </si>
+  <si>
     <t>20 micro agri-producers and 10 small and medium agri-producers benefit from the implementation of renewable energy and energy-efficient technologies (biomass boilers in greenhouses, photovoltaic, among others).</t>
-  </si>
-  <si>
-    <t>Austria (ADA) $670,123 (2024)</t>
   </si>
   <si>
     <t xml:space="preserve">1 multi-storey building and 2 social institutions </t>
@@ -405,9 +428,6 @@
   </si>
   <si>
     <t>Agricultural Services</t>
-  </si>
-  <si>
-    <t>For the policy or regulatory frameworks, the "Indicator" should refer to the unit that your targets are listed as, along with a justification as needed. The numbers showed in target are not clear what they reffered to. Need also to disagregate data for 1000378 and 133573</t>
   </si>
   <si>
     <t>Tier</t>
@@ -561,7 +581,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -613,6 +633,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFE699"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -679,7 +705,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -756,21 +782,78 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -789,12 +872,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -806,9 +883,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1115,6 +1189,482 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0B8D031-DB22-47ED-A6B4-22FC4BDA370C}">
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="38.7109375" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" customWidth="1"/>
+    <col min="4" max="4" width="39.5703125" customWidth="1"/>
+    <col min="5" max="5" width="28.42578125" customWidth="1"/>
+    <col min="6" max="6" width="65.140625" customWidth="1"/>
+    <col min="7" max="7" width="46.85546875" customWidth="1"/>
+    <col min="8" max="8" width="30.85546875" customWidth="1"/>
+    <col min="9" max="9" width="56.140625" customWidth="1"/>
+    <col min="10" max="10" width="28.28515625" customWidth="1"/>
+    <col min="11" max="11" width="32" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="306" customHeight="1">
+      <c r="A2" s="33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="8">
+        <v>127500</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="31"/>
+      <c r="H2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="252.75" customHeight="1">
+      <c r="A3" s="6"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="8">
+        <v>186950</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="31"/>
+      <c r="H3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" s="46"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="26"/>
+    </row>
+    <row r="4" spans="1:13" ht="45" customHeight="1">
+      <c r="A4" s="6"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="8">
+        <v>49000</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="31"/>
+      <c r="H4" s="7">
+        <v>5</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="46"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="94.5" customHeight="1">
+      <c r="A5" s="6"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="8">
+        <v>30000</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="31"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="46"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="13"/>
+    </row>
+    <row r="6" spans="1:13" ht="45" customHeight="1">
+      <c r="A6" s="6"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="8">
+        <v>122000</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="31"/>
+      <c r="H6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="L6" s="48"/>
+      <c r="M6" s="26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="45" customHeight="1">
+      <c r="A7" s="6"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="37">
+        <v>20000</v>
+      </c>
+      <c r="E7" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="40"/>
+      <c r="H7" s="39"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" s="48"/>
+      <c r="M7" s="26"/>
+    </row>
+    <row r="8" spans="1:13" ht="106.5" customHeight="1">
+      <c r="A8" s="6"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="37">
+        <v>56000</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="40"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" s="49"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="303.75" customHeight="1">
+      <c r="A9" s="25">
+        <v>130906</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="15">
+        <v>649000</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="30"/>
+      <c r="H9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="M9" s="13"/>
+    </row>
+    <row r="10" spans="1:13" ht="214.5" customHeight="1">
+      <c r="A10" s="25"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="14">
+        <v>730850</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="30"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" s="45"/>
+      <c r="M10" s="13"/>
+    </row>
+    <row r="11" spans="1:13" ht="214.5" customHeight="1">
+      <c r="A11" s="25"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="44">
+        <v>372900</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="30"/>
+      <c r="H11" s="6">
+        <v>200000</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J11" s="45"/>
+      <c r="M11" s="26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="214.5" customHeight="1">
+      <c r="A12" s="25"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="41">
+        <v>9039075</v>
+      </c>
+      <c r="E12" s="38"/>
+      <c r="F12" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="42"/>
+      <c r="H12" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" s="45"/>
+      <c r="M12" s="26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="214.5" customHeight="1">
+      <c r="A13" s="7">
+        <v>130906</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="22">
+        <f>9826008+6666666</f>
+        <v>16492674</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="29"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J13" s="45"/>
+      <c r="M13" s="13"/>
+    </row>
+    <row r="14" spans="1:13" ht="193.5" customHeight="1">
+      <c r="A14" s="7">
+        <v>1000378</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="8">
+        <v>2298111</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14" s="7">
+        <v>20000</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="L14" t="s">
+        <v>68</v>
+      </c>
+      <c r="M14" s="13"/>
+    </row>
+    <row r="15" spans="1:13" ht="322.5" customHeight="1">
+      <c r="A15" s="7">
+        <v>133573</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="17">
+        <v>1983621</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="36" t="s">
+        <v>73</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J15" t="s">
+        <v>75</v>
+      </c>
+      <c r="L15" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="M15" s="13"/>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="J9:J13"/>
+    <mergeCell ref="J2:J5"/>
+    <mergeCell ref="L2:L8"/>
+    <mergeCell ref="J7:J8"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E6" xr:uid="{7484386B-9BBD-476A-91F3-5AF2E4A5114B}"/>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="C14" r:id="rId1" xr:uid="{E166A882-82EE-43BA-800C-43C699F5B8AD}"/>
+    <hyperlink ref="C15" r:id="rId2" xr:uid="{F54D7698-3310-46A8-8B34-7F617E5DC071}"/>
+    <hyperlink ref="C2" r:id="rId3" xr:uid="{2FDD2CD3-4A1D-44AC-945B-AF971CA09CE4}"/>
+    <hyperlink ref="C9:C12" r:id="rId4" display="https://www.undp.org/moldova/projects/addressing-impacts-energy-crisis-republic-moldova" xr:uid="{C8AAC88F-363F-4778-A2DA-825D54C305E7}"/>
+    <hyperlink ref="C13" r:id="rId5" xr:uid="{CE989422-ABF1-46B8-AB73-AC4E686E8BD7}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C6B7439B-2465-4ED7-8B4F-5693BC613A05}">
+          <x14:formula1>
+            <xm:f>'Beneficiary Categories'!$B$2:$B$16</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E5 E7:E15</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49729D02-0BFC-449F-BFDA-CA7667244C40}">
   <dimension ref="A1:M18"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -1174,38 +1724,38 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="306" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="56" t="s">
         <v>15</v>
       </c>
       <c r="D2" s="8">
         <v>127500</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="39" t="s">
+      <c r="J2" s="46" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="32" t="s">
+      <c r="L2" s="47" t="s">
         <v>22</v>
       </c>
       <c r="M2" s="26" t="s">
@@ -1213,257 +1763,257 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="252.75" customHeight="1">
-      <c r="A3" s="34"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="38"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="57"/>
       <c r="D3" s="8">
         <v>186950</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="I3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="39"/>
-      <c r="L3" s="28"/>
+      <c r="J3" s="46"/>
+      <c r="L3" s="48"/>
       <c r="M3" s="26"/>
     </row>
     <row r="4" spans="1:13" ht="45" customHeight="1">
-      <c r="A4" s="34"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="38"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="57"/>
       <c r="D4" s="8">
         <v>49000</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G4" s="10">
         <v>2020</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J4" s="46"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="39"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="26" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="5" spans="1:13" ht="94.5" customHeight="1">
-      <c r="A5" s="34"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="38"/>
+      <c r="A5" s="53"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="57"/>
       <c r="D5" s="8">
         <v>30000</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="G5" s="10">
         <v>2019</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
-      <c r="J5" s="39"/>
-      <c r="L5" s="28"/>
+      <c r="J5" s="46"/>
+      <c r="L5" s="48"/>
       <c r="M5" s="13"/>
     </row>
     <row r="6" spans="1:13" ht="45" customHeight="1">
-      <c r="A6" s="34"/>
-      <c r="B6" s="36"/>
-      <c r="C6" s="38"/>
+      <c r="A6" s="53"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="57"/>
       <c r="D6" s="8">
         <v>122000</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>35</v>
-      </c>
       <c r="G6" s="10" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="L6" s="48"/>
+      <c r="M6" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="L6" s="28"/>
-      <c r="M6" s="26" t="s">
-        <v>39</v>
-      </c>
     </row>
     <row r="7" spans="1:13" ht="45" customHeight="1">
-      <c r="A7" s="34"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="38"/>
+      <c r="A7" s="53"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="57"/>
       <c r="D7" s="8">
         <v>20000</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="G7" s="10" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
-      <c r="J7" s="40" t="s">
+      <c r="J7" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="L7" s="28"/>
+      <c r="L7" s="48"/>
       <c r="M7" s="26"/>
     </row>
     <row r="8" spans="1:13" ht="106.5" customHeight="1">
-      <c r="A8" s="34"/>
-      <c r="B8" s="36"/>
-      <c r="C8" s="38"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="57"/>
       <c r="D8" s="8">
         <v>56000</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="J8" s="40"/>
-      <c r="L8" s="28"/>
+        <v>43</v>
+      </c>
+      <c r="J8" s="49"/>
+      <c r="L8" s="48"/>
       <c r="M8" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="303.75" customHeight="1">
-      <c r="A9" s="28">
+      <c r="A9" s="48">
         <v>130906</v>
       </c>
-      <c r="B9" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>48</v>
+      <c r="B9" s="50" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>45</v>
       </c>
       <c r="D9" s="15">
         <v>649000</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G9" s="16">
         <v>2022</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="J9" s="31" t="s">
-        <v>52</v>
+        <v>48</v>
+      </c>
+      <c r="J9" s="45" t="s">
+        <v>49</v>
       </c>
       <c r="M9" s="13"/>
     </row>
     <row r="10" spans="1:13" ht="214.5" customHeight="1">
-      <c r="A10" s="28"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="30"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="50"/>
+      <c r="C10" s="51"/>
       <c r="D10" s="14">
         <v>730850</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G10" s="16">
         <v>2022</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="J10" s="31"/>
+        <v>51</v>
+      </c>
+      <c r="J10" s="45"/>
       <c r="M10" s="13"/>
     </row>
     <row r="11" spans="1:13" ht="214.5" customHeight="1">
-      <c r="A11" s="28"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="30"/>
+      <c r="A11" s="48"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="51"/>
       <c r="D11" s="14">
         <v>372900</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G11" s="16">
         <v>2022</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J11" s="31"/>
+        <v>53</v>
+      </c>
+      <c r="J11" s="45"/>
       <c r="M11" s="26" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="214.5" customHeight="1">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="30"/>
+      <c r="A12" s="48"/>
+      <c r="B12" s="50"/>
+      <c r="C12" s="51"/>
       <c r="D12" s="14">
         <v>9039075</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G12" s="16">
         <v>2022</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="J12" s="31"/>
+        <v>57</v>
+      </c>
+      <c r="J12" s="45"/>
       <c r="M12" s="26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="214.5" customHeight="1">
@@ -1471,28 +2021,28 @@
         <v>130906</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="G13" s="18">
         <v>2022</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="J13" s="31"/>
+        <v>82</v>
+      </c>
+      <c r="J13" s="45"/>
       <c r="M13" s="13"/>
     </row>
     <row r="14" spans="1:13" ht="193.5" customHeight="1">
@@ -1500,34 +2050,34 @@
         <v>1000378</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D14" s="8">
         <v>2298111</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H14" s="5">
         <v>20000</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="J14" s="19" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L14" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M14" s="13"/>
     </row>
@@ -1537,7 +2087,7 @@
       <c r="C15" s="9"/>
       <c r="D15" s="8"/>
       <c r="E15" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -1553,34 +2103,34 @@
         <v>133573</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E16" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>72</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>76</v>
       </c>
       <c r="G16" s="4">
         <v>2022</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="L16" s="25" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M16" s="13"/>
     </row>
@@ -1626,7 +2176,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J17"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -1676,335 +2226,335 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="166.5" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="56" t="s">
         <v>15</v>
       </c>
       <c r="D2" s="8">
         <v>127500</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="J2" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="J2" s="46" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="45" customHeight="1">
-      <c r="A3" s="34"/>
-      <c r="B3" s="36"/>
-      <c r="C3" s="38"/>
+      <c r="A3" s="53"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="57"/>
       <c r="D3" s="8">
         <v>186950</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>25</v>
-      </c>
       <c r="G3" s="10" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="J3" s="39"/>
+        <v>88</v>
+      </c>
+      <c r="J3" s="46"/>
     </row>
     <row r="4" spans="1:10" ht="45" customHeight="1">
-      <c r="A4" s="34"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="38"/>
+      <c r="A4" s="53"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="57"/>
       <c r="D4" s="8">
         <v>49000</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G4" s="10">
         <v>2020</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="I4" s="4"/>
-      <c r="J4" s="39"/>
+      <c r="J4" s="46"/>
     </row>
     <row r="5" spans="1:10" ht="94.5" customHeight="1">
-      <c r="A5" s="34"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="38"/>
+      <c r="A5" s="53"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="57"/>
       <c r="D5" s="8">
         <v>30000</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="G5" s="10">
         <v>2019</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I5" s="4"/>
-      <c r="J5" s="39"/>
+      <c r="J5" s="46"/>
     </row>
     <row r="6" spans="1:10" ht="45" customHeight="1">
-      <c r="A6" s="34"/>
-      <c r="B6" s="36"/>
-      <c r="C6" s="38"/>
+      <c r="A6" s="53"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="57"/>
       <c r="D6" s="8">
         <v>122000</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="45" customHeight="1">
-      <c r="A7" s="34"/>
-      <c r="B7" s="36"/>
-      <c r="C7" s="38"/>
+      <c r="A7" s="53"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="57"/>
       <c r="D7" s="8">
         <v>20000</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="G7" s="10" t="s">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I7" s="4"/>
-      <c r="J7" s="40" t="s">
+      <c r="J7" s="49" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="61.5" customHeight="1">
-      <c r="A8" s="34"/>
-      <c r="B8" s="36"/>
-      <c r="C8" s="38"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="55"/>
+      <c r="C8" s="57"/>
       <c r="D8" s="8">
         <v>56000</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="49"/>
+    </row>
+    <row r="9" spans="1:10" ht="303.75" customHeight="1">
+      <c r="A9" s="48">
+        <v>130906</v>
+      </c>
+      <c r="B9" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="C9" s="51" t="s">
         <v>45</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="40"/>
-    </row>
-    <row r="9" spans="1:10" ht="303.75" customHeight="1">
-      <c r="A9" s="28">
-        <v>130906</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>48</v>
       </c>
       <c r="D9" s="15">
         <v>649000</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G9" s="16">
         <v>2022</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="J9" s="31" t="s">
-        <v>52</v>
+        <v>48</v>
+      </c>
+      <c r="J9" s="45" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="214.5" customHeight="1">
-      <c r="A10" s="28"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="30"/>
+      <c r="A10" s="48"/>
+      <c r="B10" s="50"/>
+      <c r="C10" s="51"/>
       <c r="D10" s="14">
         <v>730850</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G10" s="16">
         <v>2022</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I10" s="4"/>
-      <c r="J10" s="31"/>
+      <c r="J10" s="45"/>
     </row>
     <row r="11" spans="1:10" ht="214.5" customHeight="1">
-      <c r="A11" s="28"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="30"/>
+      <c r="A11" s="48"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="51"/>
       <c r="D11" s="14">
         <v>372900</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G11" s="16">
         <v>2022</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="J11" s="31"/>
+        <v>96</v>
+      </c>
+      <c r="J11" s="45"/>
     </row>
     <row r="12" spans="1:10" ht="214.5" customHeight="1">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="30"/>
+      <c r="A12" s="48"/>
+      <c r="B12" s="50"/>
+      <c r="C12" s="51"/>
       <c r="D12" s="14">
         <v>9039075</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G12" s="16">
         <v>2022</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="I12" s="45" t="s">
-        <v>93</v>
-      </c>
-      <c r="J12" s="31"/>
+        <v>97</v>
+      </c>
+      <c r="I12" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="J12" s="45"/>
     </row>
     <row r="13" spans="1:10" ht="214.5" customHeight="1">
       <c r="A13" s="7">
         <v>130906</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="G13" s="18">
         <v>2022</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="J13" s="31"/>
+        <v>82</v>
+      </c>
+      <c r="J13" s="45"/>
     </row>
     <row r="14" spans="1:10" ht="303" customHeight="1">
       <c r="A14" s="7">
         <v>1000378</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D14" s="8">
         <v>2298111</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H14" s="5">
         <v>500</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="J14" s="19" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="322.5" customHeight="1">
@@ -2012,37 +2562,35 @@
         <v>133573</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G15" s="4">
         <v>2022</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="12" t="s">
-        <v>96</v>
-      </c>
+      <c r="A17" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2079,7 +2627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
@@ -2089,160 +2637,160 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="41" t="s">
-        <v>99</v>
+      <c r="A2" s="58" t="s">
+        <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="58"/>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="58"/>
+      <c r="B4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="41"/>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="41"/>
-      <c r="B4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" t="s">
-        <v>95</v>
-      </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="42"/>
+      <c r="A6" s="59"/>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="42"/>
+      <c r="A7" s="59"/>
       <c r="B7" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="42"/>
+      <c r="A8" s="59"/>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="42"/>
+      <c r="A9" s="59"/>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="43" t="s">
-        <v>113</v>
+      <c r="A10" s="60" t="s">
+        <v>117</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="43"/>
+      <c r="A11" s="60"/>
       <c r="B11" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="44" t="s">
-        <v>117</v>
+      <c r="A12" s="61" t="s">
+        <v>121</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="44"/>
+      <c r="A13" s="61"/>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="44"/>
+      <c r="A14" s="61"/>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -2257,6 +2805,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -2505,28 +3073,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36D49E0E-D524-40C8-9640-978549F64A96}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1FA3D7F-F698-4E68-A900-C45E704A4D7C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2534,5 +3082,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1FA3D7F-F698-4E68-A900-C45E704A4D7C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36D49E0E-D524-40C8-9640-978549F64A96}"/>
 </file>
--- a/01_Input/00_CO Validation/Moldova Republic - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Moldova Republic - Energy Projects.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ben/Documents/UNDP/Energy/CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="847" documentId="13_ncr:1_{F7DA749C-5740-5D4C-B662-A29A9599CDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BEA07B9-7A79-4AF0-8E77-45D7F3F10EB2}"/>
+  <xr:revisionPtr revIDLastSave="849" documentId="13_ncr:1_{F7DA749C-5740-5D4C-B662-A29A9599CDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A2853B9-61EC-4018-AED7-CE707491B8CE}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="740" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3495,28 +3495,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0d2b1cfbe0bead55dc04bff20486709a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3ed273af6605fa6a207dd3965c2d078" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
     <xsd:import namespace="fb9e4d32-074f-4c04-81ef-e811753dfd59"/>
     <xsd:element name="properties">
@@ -3541,6 +3521,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -3620,6 +3601,11 @@
     <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -3763,8 +3749,28 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1FA3D7F-F698-4E68-A900-C45E704A4D7C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16E1EE50-1E76-4669-A00C-97DB2E2DCEF9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3772,5 +3778,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36D49E0E-D524-40C8-9640-978549F64A96}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1FA3D7F-F698-4E68-A900-C45E704A4D7C}"/>
 </file>
--- a/01_Input/00_CO Validation/Moldova Republic - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Moldova Republic - Energy Projects.xlsx
@@ -1,23 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28627"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ben/Documents/UNDP/Energy/CO Validation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://undp.sharepoint.com/sites/UNDPSustainableEnergyHub/Shared Documents/General/0. CURRENT FOLDER - Sustainable Energy Hub/05. Accounting for Progress to 500M/7. CO Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="849" documentId="13_ncr:1_{F7DA749C-5740-5D4C-B662-A29A9599CDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A2853B9-61EC-4018-AED7-CE707491B8CE}"/>
+  <xr:revisionPtr revIDLastSave="1104" documentId="13_ncr:1_{F7DA749C-5740-5D4C-B662-A29A9599CDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{861D363B-CEF6-4E28-9804-331D9E22095D}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="740" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-150" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projects (3)" sheetId="4" r:id="rId1"/>
-    <sheet name="Projects (2)" sheetId="3" r:id="rId2"/>
-    <sheet name="Projects" sheetId="1" r:id="rId3"/>
+    <sheet name="Projects (2)" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="Projects" sheetId="1" state="hidden" r:id="rId3"/>
     <sheet name="Beneficiary Categories" sheetId="2" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Projects (3)'!$A$1:$AF$1</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="191">
   <si>
     <t>Project ID</t>
   </si>
@@ -102,6 +105,9 @@
   </si>
   <si>
     <t>Policy Population</t>
+  </si>
+  <si>
+    <t>prodoc</t>
   </si>
   <si>
     <t>5492 / 00101330</t>
@@ -314,9 +320,6 @@
     <t xml:space="preserve">Energy Vulnerability Reduction Fund </t>
   </si>
   <si>
-    <t>Addressing the impacts of the energy crisis in the Republic of Moldova | United Nations Development Programme (undp.org)</t>
-  </si>
-  <si>
     <t>Support with defining “energy vulnerable consumer” ​
 Support with drafting of the Law on the Fund for Reduction of Energy Vulnerability (Law 241/2022) in Moldova
 Support with establishment of the Energy Vulnerability Fund;​
@@ -377,15 +380,163 @@
     <t>SMEs, vulnerable small farmers (particularly women-led farms and young people) in rural areas</t>
   </si>
   <si>
-    <t xml:space="preserve">30
+    <t>To enhance women agri-producer's resilience in the context of the socio-economic, climate and energys crisis in Moldova</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83
 </t>
   </si>
   <si>
-    <t>20 micro agri-producers and 10 small and medium agri-producers benefit from the implementation of renewable energy and energy-efficient technologies (biomass boilers in greenhouses, photovoltaic, among others).
-US$1,983,621 ($689,308 managed by UNDP)</t>
-  </si>
-  <si>
-    <t>Austria (ADA) $670,123 (2024)</t>
+    <t>47 micro agri-producers and 36 small and medium agri-producers benefit from the implementation of renewable energy and energy-efficient technologies (biomass boilers in greenhouses, photovoltaic, among others).
+US$4,150.139 ($1,447.590 managed by UNDP)</t>
+  </si>
+  <si>
+    <t>Austria (ADA) $ 455,455.53 (2024)
+Switzerland (SDC)$ 986,845.96 (2024)</t>
+  </si>
+  <si>
+    <t>The target qroup are 100% women 
+agri-producers</t>
+  </si>
+  <si>
+    <t>Community</t>
+  </si>
+  <si>
+    <t>Greening the future, advancing rights and stability: spurring an inclusive and green transition with responsive governance in the eastern neighbourhood region (Molodva)</t>
+  </si>
+  <si>
+    <t>https://www.undp.org/moldova/projects/greening-future-advancing-rights-and-stability-spurring-inclusive-and-green-transition-responsive-governance-eastern-neighbourhood</t>
+  </si>
+  <si>
+    <t>4.1.2.Number of co-designed risk-informed regulatory and policy frameworks on climate change, disaster risk reduction, environment and energy
+4.2.1. Number of people with access to clean, affordable and sustainable energy
+4.2.4. Number of partnerships with private sector to promote and co-design innovative solutions on renewable energy, low emission, climate resilient and green development
+4.3.3. Number of non-governmental organizations (NGOs)/CBOs with capacities to engage in the areas of climate resilience, low emission and green development</t>
+  </si>
+  <si>
+    <t>4.1.2. Baseline: 4 
+4.2.1. Baseline: total 199,030 (Women: 53,738 (27%) Men: 145,291) 
+4.2.4. Baseline: 29 
+4.3.3. Baseline: 116</t>
+  </si>
+  <si>
+    <t>4.1.2. Target: 7
+4.2.1.  Target: 215,000 (Women: 64,500/Men: 150,500)
+4.2.4. Target: 34
+4.3.3.Target: 130</t>
+  </si>
+  <si>
+    <t>Expected results:
+- National Centre for Sustainable Energy has enhanced proficiency in funding and executing energy efficiency projects in the residential buildings
+- National energy related campaigns are complemented by nudging strategies and behavioural change initiatives to encourage energy efficiency practices
+- At least 5 energy audit of residential buildings are conducted and at least 2 technical designs completedBroadened access for private companies to green and low-carbon technologies available in the national market;
+- A targeted energy audit program for MSMEs to engage in energy-saving and greenhouse gas emission reduction practices is launched
+- At least 10 regulatory acts in transportation sector 
+- Support provided to certain elements of digitalization process of road transportation sector</t>
+  </si>
+  <si>
+    <t>Denmark: 2024	= $1,217,005, 2025 = $1,887,018, 2026 = $910,065, 2027 = $254,178</t>
+  </si>
+  <si>
+    <t>Accelerating a Just Transition in the Republic of Moldova Programme</t>
+  </si>
+  <si>
+    <t>https://www.undp.org/moldova/projects/accelerating-just-transition-republic-moldova-programme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I1 Number of people reached through public awareness campaign outreach on energy efficiency and differentiated tariff benefits (out of which at least 40% women)
+I2 Number of representatives participating in workshops on differentiated tariffs provided with educational materials
+I3 Number of households and public sector entities with installed smart metering infrastructure for electricity
+I4 Number of households/apartments in multi-apartment buildings (MAB) with installed smart thermal energy metering infrastructure
+I5 Number of established unified National Consumer Location ID Register (RNLC)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,000,000 consumers outreach (40% women)
+60,000 consumers (households )
+4
+1
+3,000,000 people (40% women)
+50 journalists, system operators, institutions, and civil society representatives
+60,000 households, prosumers, and public sector entities
+1,500 households/apartments in MAB
+1 established unified RNLC
+</t>
+  </si>
+  <si>
+    <t>Italy: 2024 = $7,813,710, 2025 = $3,151,201
+Sweden: 2024 = $9,560,229.01</t>
+  </si>
+  <si>
+    <t>Government Capacity-Building</t>
+  </si>
+  <si>
+    <t>Resilient Communities through Women Empowerment, phase II</t>
+  </si>
+  <si>
+    <t>https://www.undp.org/moldova/projects/resilient-communities-through-women-empowerment-phase-2</t>
+  </si>
+  <si>
+    <t>Level of awareness on gender transformative climate change interventions in pilot communities as a result of project interventions
+No. of LPAs that developed and apply SECAPs with integrated gender aspects
+Number of policy recommendations or other central government actions actively promoted in these fora
+Number of business incubators benefiting from capacity building and institutional support on gender &amp; climate
+Number of women benefiting from implemented community grants financed by the project 
+Number of household women who improved their resilience due to climate change adaptation/mitigation activities</t>
+  </si>
+  <si>
+    <t>TBD
+68
+0
+0
+0
+0</t>
+  </si>
+  <si>
+    <t>70% of the target beneficiaries are aware of gender transformative climate change interventions
+83 
+6
+12
+30,000
+80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweden: 2024 = $182,338.04, 2025 = $1,689,690.26, 2026 = $1,686,532.06, 2027 = $1,137,162.54, 2028 = $299,093.38
+Norway: 2024 = $592,708.17, 2025 = $1,063,419.99, 2026 = $747,128,23	 </t>
+  </si>
+  <si>
+    <t>Most of the direct and indirect
+ beneficiaries are women mainly consisting in provision of dedicated technical and financial assistance for putting in place climate resilient agri-practices</t>
+  </si>
+  <si>
+    <t>Enabling an Inclusive Green Transition in the Republic of Moldova</t>
+  </si>
+  <si>
+    <t>https://open.undp.org/projects/01001335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3 Private investment attracted to green and eco-innovation projects
+1.5 Number of green jobs supported/sustained
+1.1.1 Number of public officials who participated in platforms, research and events
+1.1.2 Number of civisl society representatives who participated in the platforms and events
+1.1.3 Number of other participants of the platforms and events
+1.1.7 National Sustainable Mobility Programme and Action Plan developed
+2.1.2 Number of people benefiting from capacity building programme on the green transition
+3.1.3 Number of green start-ups
+</t>
+  </si>
+  <si>
+    <t>1.3 Target: 1,000,000 EUR additional investment
+1.5 Target: 150 new jobs
+1.1.1 Target: 50, including 40% women
+1.1.2 Target: 25, including 30% women
+1.1.3 Target: 25
+1.1.7 Target: National Sustainable Mobility Programme and Action Plan developed
+2.1.2 Target: 100, including 50% women
+3.1.3 Target: 3 eco-mobility startups supported</t>
+  </si>
+  <si>
+    <t>Note: project data added by Yevgen on 21 Nov 2024</t>
   </si>
   <si>
     <t>Category</t>
@@ -422,6 +573,9 @@
   </si>
   <si>
     <t>to the CO: Please estimate number of beneficiaries / participants in the campaign</t>
+  </si>
+  <si>
+    <t>Addressing the impacts of the energy crisis in the Republic of Moldova | United Nations Development Programme (undp.org)</t>
   </si>
   <si>
     <t xml:space="preserve">2023:
@@ -438,7 +592,14 @@
     <t>US$1,983,621 ($689,308 managed by UNDP)</t>
   </si>
   <si>
+    <t xml:space="preserve">30
+</t>
+  </si>
+  <si>
     <t>20 micro agri-producers and 10 small and medium agri-producers benefit from the implementation of renewable energy and energy-efficient technologies (biomass boilers in greenhouses, photovoltaic, among others).</t>
+  </si>
+  <si>
+    <t>Austria (ADA) $670,123 (2024)</t>
   </si>
   <si>
     <t xml:space="preserve">1 multi-storey building and 2 social institutions </t>
@@ -616,7 +777,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -693,6 +854,13 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -720,7 +888,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -850,14 +1018,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -948,9 +1130,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -999,9 +1178,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1049,6 +1225,84 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1103,7 +1357,7 @@
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1406,7 +1660,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0B8D031-DB22-47ED-A6B4-22FC4BDA370C}">
-  <dimension ref="A1:AE17"/>
+  <dimension ref="A1:AF20"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1416,526 +1670,528 @@
     <col min="5" max="5" width="28.42578125" customWidth="1"/>
     <col min="6" max="6" width="65.140625" customWidth="1"/>
     <col min="7" max="7" width="46.85546875" customWidth="1"/>
-    <col min="8" max="8" width="30.85546875" customWidth="1"/>
+    <col min="8" max="8" width="45.140625" customWidth="1"/>
     <col min="9" max="9" width="56.140625" customWidth="1"/>
     <col min="10" max="10" width="28.28515625" customWidth="1"/>
     <col min="11" max="11" width="32" customWidth="1"/>
-    <col min="12" max="12" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="30.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="28.28515625" customWidth="1"/>
+    <col min="19" max="19" width="15" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:31" ht="31.5" customHeight="1">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="G1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="60" t="s">
+      <c r="J1" s="59" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="K1" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="52" t="s">
+      <c r="L1" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="68" t="s">
+      <c r="M1" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="52" t="s">
+      <c r="N1" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="52" t="s">
+      <c r="O1" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="68" t="s">
+      <c r="P1" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="68" t="s">
+      <c r="Q1" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="69" t="s">
+      <c r="R1" s="68" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="60" t="s">
+      <c r="S1" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="69" t="s">
+      <c r="T1" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="60" t="s">
+      <c r="U1" s="59" t="s">
         <v>20</v>
       </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2" spans="1:31" ht="306" customHeight="1">
-      <c r="A2" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="29" t="s">
+      <c r="A2" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="B2" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="31">
+      <c r="C2" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="32">
         <v>127500</v>
       </c>
-      <c r="E2" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="28" t="s">
+      <c r="E2" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="28" t="s">
+      <c r="F2" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="I2" s="57" t="s">
+      <c r="G2" s="33"/>
+      <c r="H2" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="61" t="s">
+      <c r="I2" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="58" t="s">
+      <c r="J2" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="70" t="s">
+      <c r="K2" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="M2" s="33"/>
-      <c r="N2" s="71" t="s">
+      <c r="L2" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
       <c r="S2" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="T2" s="33"/>
+        <v>33</v>
+      </c>
+      <c r="T2" s="1"/>
       <c r="U2" s="39"/>
-      <c r="Y2" s="72" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z2" s="53"/>
-      <c r="AA2" s="28" t="s">
-        <v>30</v>
+      <c r="Y2" s="99" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z2" s="52"/>
+      <c r="AA2" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="AB2" s="34"/>
       <c r="AC2" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD2" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE2" s="1"/>
+    </row>
+    <row r="3" spans="1:31" ht="252.75" customHeight="1">
+      <c r="A3" s="29"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32">
+        <v>186950</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="33"/>
+      <c r="H3" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="56" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="61"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="AD2" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="AE2" s="33"/>
-    </row>
-    <row r="3" spans="1:31" ht="252.75" customHeight="1">
-      <c r="A3" s="28"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="31">
-        <v>186950</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="32"/>
-      <c r="H3" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" s="57" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" s="62"/>
-      <c r="K3" s="59"/>
-      <c r="L3" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" s="33"/>
-      <c r="N3" s="71" t="s">
+      <c r="M3" s="1"/>
+      <c r="N3" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="T3" s="1"/>
+      <c r="U3" s="39"/>
+      <c r="Y3" s="99"/>
+      <c r="Z3" s="52"/>
+      <c r="AA3" s="29" t="s">
         <v>31</v>
-      </c>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="33"/>
-      <c r="R3" s="33"/>
-      <c r="S3" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="T3" s="33"/>
-      <c r="U3" s="39"/>
-      <c r="Y3" s="72"/>
-      <c r="Z3" s="53"/>
-      <c r="AA3" s="28" t="s">
-        <v>30</v>
       </c>
       <c r="AB3" s="34"/>
       <c r="AC3" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD3" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE3" s="1"/>
+    </row>
+    <row r="4" spans="1:31" ht="45" customHeight="1">
+      <c r="A4" s="29"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="32">
+        <v>49000</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="33"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="56" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="61"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="AD3" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="AE3" s="33"/>
-    </row>
-    <row r="4" spans="1:31" ht="45" customHeight="1">
-      <c r="A4" s="28"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="31">
-        <v>49000</v>
-      </c>
-      <c r="E4" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="32"/>
-      <c r="H4" s="29">
-        <v>5</v>
-      </c>
-      <c r="I4" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="62"/>
-      <c r="K4" s="59"/>
-      <c r="L4" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="M4" s="33"/>
-      <c r="N4" s="71" t="s">
+      <c r="M4" s="1"/>
+      <c r="N4" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="1"/>
+      <c r="U4" s="39"/>
+      <c r="Y4" s="99"/>
+      <c r="Z4" s="52"/>
+      <c r="AA4" s="29" t="s">
         <v>31</v>
-      </c>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="T4" s="33"/>
-      <c r="U4" s="39"/>
-      <c r="Y4" s="72"/>
-      <c r="Z4" s="53"/>
-      <c r="AA4" s="28" t="s">
-        <v>30</v>
       </c>
       <c r="AB4" s="34"/>
       <c r="AC4" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD4" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE4" s="1"/>
+    </row>
+    <row r="5" spans="1:31" ht="105">
+      <c r="A5" s="29"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="32">
+        <v>30000</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="33"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="58"/>
+      <c r="L5" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="AD4" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="AE4" s="33"/>
-    </row>
-    <row r="5" spans="1:31" ht="106.5">
-      <c r="A5" s="28"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="31">
-        <v>30000</v>
-      </c>
-      <c r="E5" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="32"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="59"/>
-      <c r="L5" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="M5" s="33"/>
-      <c r="N5" s="71" t="s">
-        <v>31</v>
-      </c>
-      <c r="O5" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="R5" s="33" t="s">
+      <c r="M5" s="1"/>
+      <c r="N5" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="R5" s="1" t="s">
+        <v>44</v>
+      </c>
       <c r="S5" s="39"/>
-      <c r="T5" s="33" t="s">
-        <v>44</v>
+      <c r="T5" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="U5" s="39">
         <v>487707</v>
       </c>
-      <c r="Y5" s="72"/>
-      <c r="Z5" s="53"/>
-      <c r="AA5" s="28" t="s">
-        <v>30</v>
+      <c r="Y5" s="99"/>
+      <c r="Z5" s="52"/>
+      <c r="AA5" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="AB5" s="34"/>
       <c r="AC5" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD5" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE5" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" ht="45" customHeight="1">
+      <c r="A6" s="29"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="32">
+        <v>122000</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="33"/>
+      <c r="H6" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" s="63" t="s">
+        <v>51</v>
+      </c>
+      <c r="K6" s="34"/>
+      <c r="L6" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="AD5" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="AE5" s="33" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" ht="45" customHeight="1">
-      <c r="A6" s="28"/>
-      <c r="B6" s="29"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="31">
-        <v>122000</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="32"/>
-      <c r="H6" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="I6" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="J6" s="64" t="s">
-        <v>50</v>
-      </c>
-      <c r="K6" s="34"/>
-      <c r="L6" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6" s="33"/>
-      <c r="N6" s="71" t="s">
+      <c r="M6" s="1"/>
+      <c r="N6" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="39"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="39"/>
+      <c r="Y6" s="99"/>
+      <c r="Z6" s="52"/>
+      <c r="AA6" s="29" t="s">
         <v>31</v>
-      </c>
-      <c r="O6" s="33"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="33"/>
-      <c r="S6" s="39"/>
-      <c r="T6" s="33"/>
-      <c r="U6" s="39"/>
-      <c r="Y6" s="72"/>
-      <c r="Z6" s="53"/>
-      <c r="AA6" s="28" t="s">
-        <v>30</v>
       </c>
       <c r="AB6" s="34"/>
       <c r="AC6" s="34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AD6" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE6" s="33"/>
+        <v>25</v>
+      </c>
+      <c r="AE6" s="1"/>
     </row>
     <row r="7" spans="1:31" ht="45" customHeight="1">
-      <c r="A7" s="28"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="30"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="31"/>
       <c r="D7" s="35">
         <v>20000</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G7" s="38"/>
       <c r="H7" s="37"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="66" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="59"/>
-      <c r="L7" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="M7" s="33"/>
-      <c r="N7" s="71" t="s">
+      <c r="I7" s="56"/>
+      <c r="J7" s="65" t="s">
+        <v>29</v>
+      </c>
+      <c r="K7" s="58"/>
+      <c r="L7" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="O7" s="33"/>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="33"/>
-      <c r="R7" s="33"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
       <c r="S7" s="39"/>
-      <c r="T7" s="33"/>
+      <c r="T7" s="1"/>
       <c r="U7" s="39"/>
-      <c r="Y7" s="72"/>
-      <c r="Z7" s="53"/>
-      <c r="AA7" s="28" t="s">
-        <v>30</v>
+      <c r="Y7" s="99"/>
+      <c r="Z7" s="52"/>
+      <c r="AA7" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="AB7" s="34"/>
       <c r="AC7" s="34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AD7" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE7" s="33"/>
+        <v>25</v>
+      </c>
+      <c r="AE7" s="1"/>
     </row>
     <row r="8" spans="1:31" ht="106.5" customHeight="1">
-      <c r="A8" s="28"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="30"/>
+      <c r="A8" s="29"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="31"/>
       <c r="D8" s="35">
         <v>56000</v>
       </c>
       <c r="E8" s="36" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G8" s="38"/>
       <c r="H8" s="37"/>
-      <c r="I8" s="57" t="s">
-        <v>55</v>
-      </c>
-      <c r="J8" s="67"/>
-      <c r="K8" s="59"/>
-      <c r="L8" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="M8" s="33"/>
-      <c r="N8" s="71" t="s">
+      <c r="I8" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="66"/>
+      <c r="K8" s="58"/>
+      <c r="L8" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
       <c r="S8" s="39"/>
-      <c r="T8" s="33"/>
+      <c r="T8" s="1"/>
       <c r="U8" s="39"/>
-      <c r="Y8" s="72"/>
-      <c r="Z8" s="53"/>
-      <c r="AA8" s="28" t="s">
-        <v>30</v>
+      <c r="Y8" s="99"/>
+      <c r="Z8" s="52"/>
+      <c r="AA8" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="AB8" s="34"/>
       <c r="AC8" s="34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AD8" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE8" s="33"/>
+        <v>25</v>
+      </c>
+      <c r="AE8" s="1"/>
     </row>
     <row r="9" spans="1:31" ht="303.75" customHeight="1">
       <c r="A9" s="39">
         <v>130906</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9" s="41" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D9" s="42">
         <v>649000</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="28" t="s">
-        <v>58</v>
+      <c r="F9" s="29" t="s">
+        <v>59</v>
       </c>
       <c r="G9" s="43"/>
-      <c r="H9" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="I9" s="28" t="s">
+      <c r="H9" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="J9" s="65" t="s">
+      <c r="I9" s="29" t="s">
         <v>61</v>
       </c>
+      <c r="J9" s="64" t="s">
+        <v>62</v>
+      </c>
       <c r="K9" s="34"/>
-      <c r="L9" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="M9" s="33"/>
-      <c r="N9" s="71" t="s">
+      <c r="L9" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="O9" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="33" t="s">
+      <c r="M9" s="1"/>
+      <c r="N9" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="O9" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="R9" s="33" t="s">
-        <v>24</v>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="S9" s="39"/>
-      <c r="T9" s="33" t="s">
-        <v>64</v>
+      <c r="T9" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="U9" s="39"/>
       <c r="Y9" s="34"/>
-      <c r="Z9" s="53"/>
-      <c r="AA9" s="28" t="s">
-        <v>30</v>
+      <c r="Z9" s="52"/>
+      <c r="AA9" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="AB9" s="34"/>
       <c r="AC9" s="34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD9" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE9" s="33" t="s">
-        <v>66</v>
+        <v>25</v>
+      </c>
+      <c r="AE9" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="214.5" customHeight="1">
@@ -1945,47 +2201,47 @@
       <c r="D10" s="44">
         <v>730850</v>
       </c>
-      <c r="E10" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="F10" s="28" t="s">
+      <c r="E10" s="30" t="s">
         <v>68</v>
       </c>
+      <c r="F10" s="29" t="s">
+        <v>69</v>
+      </c>
       <c r="G10" s="43"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="J10" s="54"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="J10" s="53"/>
       <c r="K10" s="34"/>
-      <c r="L10" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="M10" s="33"/>
-      <c r="N10" s="71" t="s">
+      <c r="L10" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
       <c r="S10" s="39"/>
-      <c r="T10" s="33"/>
+      <c r="T10" s="1"/>
       <c r="U10" s="39"/>
       <c r="Y10" s="34"/>
-      <c r="Z10" s="53"/>
-      <c r="AA10" s="28" t="s">
-        <v>30</v>
+      <c r="Z10" s="52"/>
+      <c r="AA10" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="AB10" s="34"/>
       <c r="AC10" s="34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AD10" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE10" s="33" t="s">
-        <v>45</v>
+        <v>25</v>
+      </c>
+      <c r="AE10" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="214.5" customHeight="1">
@@ -1995,48 +2251,48 @@
       <c r="D11" s="45">
         <v>372900</v>
       </c>
-      <c r="E11" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" s="28" t="s">
-        <v>70</v>
+      <c r="E11" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>71</v>
       </c>
       <c r="G11" s="43"/>
-      <c r="H11" s="28">
+      <c r="H11" s="29">
         <v>200000</v>
       </c>
-      <c r="I11" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="J11" s="54"/>
+      <c r="I11" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="J11" s="53"/>
       <c r="K11" s="34"/>
-      <c r="L11" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="M11" s="33"/>
-      <c r="N11" s="71" t="s">
+      <c r="L11" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="33"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
       <c r="S11" s="39"/>
-      <c r="T11" s="33"/>
+      <c r="T11" s="1"/>
       <c r="U11" s="39"/>
       <c r="Y11" s="34"/>
-      <c r="Z11" s="53"/>
-      <c r="AA11" s="28" t="s">
-        <v>30</v>
+      <c r="Z11" s="52"/>
+      <c r="AA11" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="AB11" s="34"/>
       <c r="AC11" s="34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AD11" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE11" s="33"/>
+        <v>25</v>
+      </c>
+      <c r="AE11" s="1"/>
     </row>
     <row r="12" spans="1:31" ht="214.5" customHeight="1">
       <c r="A12" s="39"/>
@@ -2046,276 +2302,523 @@
         <v>9039075</v>
       </c>
       <c r="E12" s="36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G12" s="47"/>
       <c r="H12" s="37" t="s">
-        <v>74</v>
-      </c>
-      <c r="I12" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="J12" s="54"/>
+      <c r="I12" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="J12" s="53"/>
       <c r="K12" s="34"/>
-      <c r="L12" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="M12" s="33"/>
-      <c r="N12" s="71" t="s">
+      <c r="L12" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="O12" s="33"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="33"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
       <c r="S12" s="39"/>
-      <c r="T12" s="33"/>
+      <c r="T12" s="1"/>
       <c r="U12" s="39"/>
       <c r="Y12" s="34"/>
-      <c r="Z12" s="53"/>
-      <c r="AA12" s="28" t="s">
-        <v>30</v>
+      <c r="Z12" s="52"/>
+      <c r="AA12" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="AB12" s="34"/>
       <c r="AC12" s="34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AD12" s="34" t="s">
-        <v>76</v>
-      </c>
-      <c r="AE12" s="33"/>
+        <v>77</v>
+      </c>
+      <c r="AE12" s="1"/>
     </row>
     <row r="13" spans="1:31" ht="214.5" customHeight="1">
-      <c r="A13" s="29">
+      <c r="A13" s="30">
         <v>130906</v>
       </c>
-      <c r="B13" s="28" t="s">
-        <v>77</v>
+      <c r="B13" s="29" t="s">
+        <v>78</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="D13" s="49">
         <f>9826008+6666666</f>
         <v>16492674</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="E13" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="28" t="s">
+      <c r="F13" s="29" t="s">
         <v>79</v>
       </c>
       <c r="G13" s="50"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="28" t="s">
+      <c r="H13" s="30"/>
+      <c r="I13" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="J13" s="54"/>
+      <c r="J13" s="53"/>
       <c r="K13" s="34"/>
-      <c r="L13" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="M13" s="33"/>
-      <c r="N13" s="71" t="s">
+      <c r="L13" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="O13" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33" t="s">
+      <c r="M13" s="1"/>
+      <c r="N13" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="R13" s="33" t="s">
-        <v>24</v>
+      <c r="R13" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="S13" s="39"/>
-      <c r="T13" s="33" t="s">
-        <v>64</v>
+      <c r="T13" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="U13" s="39"/>
       <c r="Y13" s="34"/>
-      <c r="Z13" s="53"/>
-      <c r="AA13" s="28" t="s">
-        <v>30</v>
+      <c r="Z13" s="52"/>
+      <c r="AA13" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="AB13" s="34"/>
       <c r="AC13" s="34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AD13" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE13" s="33" t="s">
-        <v>66</v>
+        <v>25</v>
+      </c>
+      <c r="AE13" s="1" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="193.5" customHeight="1">
-      <c r="A14" s="29">
+      <c r="A14" s="30">
         <v>1000378</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <v>2298111</v>
       </c>
-      <c r="E14" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="28" t="s">
+      <c r="E14" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="G14" s="28" t="s">
+      <c r="G14" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="30">
         <v>20000</v>
       </c>
-      <c r="I14" s="28" t="s">
+      <c r="I14" s="29" t="s">
         <v>86</v>
       </c>
       <c r="J14" s="40" t="s">
         <v>87</v>
       </c>
       <c r="K14" s="34"/>
-      <c r="L14" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="M14" s="33"/>
-      <c r="N14" s="71" t="s">
+      <c r="L14" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="33"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
       <c r="S14" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="T14" s="33"/>
+      <c r="T14" s="1"/>
       <c r="U14" s="39"/>
       <c r="Y14" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z14" s="53"/>
-      <c r="AA14" s="28" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="Z14" s="52"/>
+      <c r="AA14" s="29" t="s">
+        <v>31</v>
       </c>
       <c r="AB14" s="34"/>
       <c r="AC14" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD14" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE14" s="1"/>
+    </row>
+    <row r="15" spans="1:31" ht="322.5" customHeight="1">
+      <c r="A15" s="72">
+        <v>133573</v>
+      </c>
+      <c r="B15" s="73" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="74" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="75">
+        <v>4150139</v>
+      </c>
+      <c r="E15" s="72" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" s="73" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" s="73" t="s">
+        <v>93</v>
+      </c>
+      <c r="H15" s="76" t="s">
+        <v>94</v>
+      </c>
+      <c r="I15" s="73" t="s">
+        <v>95</v>
+      </c>
+      <c r="J15" s="98" t="s">
+        <v>96</v>
+      </c>
+      <c r="K15" s="98" t="s">
+        <v>97</v>
+      </c>
+      <c r="L15" s="77" t="s">
         <v>31</v>
       </c>
-      <c r="AD14" s="34" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE14" s="33"/>
-    </row>
-    <row r="15" spans="1:31" ht="322.5" customHeight="1">
-      <c r="A15" s="29">
-        <v>133573</v>
-      </c>
-      <c r="B15" s="28" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" s="44">
-        <v>1983621</v>
-      </c>
-      <c r="E15" s="29" t="s">
+      <c r="M15" s="78"/>
+      <c r="N15" s="79" t="s">
+        <v>32</v>
+      </c>
+      <c r="O15" s="78" t="s">
+        <v>77</v>
+      </c>
+      <c r="P15" s="78"/>
+      <c r="Q15" s="78"/>
+      <c r="R15" s="78" t="s">
+        <v>35</v>
+      </c>
+      <c r="S15" s="80" t="s">
+        <v>33</v>
+      </c>
+      <c r="T15" s="78" t="s">
+        <v>98</v>
+      </c>
+      <c r="U15" s="80"/>
+      <c r="Y15" s="80" t="s">
+        <v>31</v>
+      </c>
+      <c r="Z15" s="89"/>
+      <c r="AA15" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB15" s="65"/>
+      <c r="AC15" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="AD15" s="65" t="s">
+        <v>35</v>
+      </c>
+      <c r="AE15" s="78"/>
+    </row>
+    <row r="16" spans="1:31" ht="322.5" customHeight="1">
+      <c r="A16" s="81">
+        <v>1001727</v>
+      </c>
+      <c r="B16" s="82" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="83" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="91">
+        <v>4268266</v>
+      </c>
+      <c r="E16" s="82" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="82" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="82" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" s="84" t="s">
+        <v>103</v>
+      </c>
+      <c r="I16" s="82" t="s">
+        <v>104</v>
+      </c>
+      <c r="J16" s="82" t="s">
+        <v>105</v>
+      </c>
+      <c r="K16" s="85"/>
+      <c r="L16" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="M16" s="86"/>
+      <c r="N16" s="87" t="s">
+        <v>32</v>
+      </c>
+      <c r="O16" s="86" t="s">
+        <v>77</v>
+      </c>
+      <c r="P16" s="86"/>
+      <c r="Q16" s="86" t="s">
+        <v>64</v>
+      </c>
+      <c r="R16" s="86" t="s">
+        <v>35</v>
+      </c>
+      <c r="S16" s="88"/>
+      <c r="T16" s="86" t="s">
+        <v>65</v>
+      </c>
+      <c r="U16" s="88"/>
+      <c r="Y16" s="88"/>
+      <c r="Z16" s="90"/>
+      <c r="AA16" s="82"/>
+      <c r="AB16" s="85"/>
+      <c r="AC16" s="85"/>
+      <c r="AD16" s="85"/>
+      <c r="AE16" s="86"/>
+    </row>
+    <row r="17" spans="1:32" ht="322.5" customHeight="1">
+      <c r="A17" s="81">
+        <v>1000952</v>
+      </c>
+      <c r="B17" s="82" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="83" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="91">
+        <v>20675141</v>
+      </c>
+      <c r="E17" s="82" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="82" t="s">
+        <v>108</v>
+      </c>
+      <c r="G17" s="82">
+        <v>0</v>
+      </c>
+      <c r="H17" s="97" t="s">
+        <v>109</v>
+      </c>
+      <c r="I17" s="82"/>
+      <c r="J17" s="82" t="s">
+        <v>110</v>
+      </c>
+      <c r="K17" s="85"/>
+      <c r="L17" s="86" t="s">
+        <v>31</v>
+      </c>
+      <c r="M17" s="86"/>
+      <c r="N17" s="87" t="s">
+        <v>32</v>
+      </c>
+      <c r="O17" s="86" t="s">
+        <v>35</v>
+      </c>
+      <c r="P17" s="86"/>
+      <c r="Q17" s="86" t="s">
+        <v>111</v>
+      </c>
+      <c r="R17" s="86" t="s">
+        <v>77</v>
+      </c>
+      <c r="S17" s="88"/>
+      <c r="T17" s="86" t="s">
+        <v>65</v>
+      </c>
+      <c r="U17" s="88"/>
+      <c r="Y17" s="88"/>
+      <c r="Z17" s="90"/>
+      <c r="AA17" s="82"/>
+      <c r="AB17" s="85"/>
+      <c r="AC17" s="85"/>
+      <c r="AD17" s="85"/>
+      <c r="AE17" s="86"/>
+    </row>
+    <row r="18" spans="1:32" ht="322.5" customHeight="1">
+      <c r="A18" s="81">
+        <v>1002849</v>
+      </c>
+      <c r="B18" s="82" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" s="83" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" s="93">
+        <v>8461359</v>
+      </c>
+      <c r="E18" s="82" t="s">
         <v>91</v>
       </c>
-      <c r="F15" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="G15" s="28"/>
-      <c r="H15" s="51" t="s">
-        <v>93</v>
-      </c>
-      <c r="I15" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="J15" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="K15" s="34"/>
-      <c r="L15" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="M15" s="33"/>
-      <c r="N15" s="71" t="s">
+      <c r="F18" s="82" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18" s="82" t="s">
+        <v>115</v>
+      </c>
+      <c r="H18" s="97" t="s">
+        <v>116</v>
+      </c>
+      <c r="I18" s="82"/>
+      <c r="J18" s="82" t="s">
+        <v>117</v>
+      </c>
+      <c r="K18" s="82" t="s">
+        <v>118</v>
+      </c>
+      <c r="L18" s="86" t="s">
         <v>31</v>
       </c>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="33"/>
-      <c r="S15" s="39"/>
-      <c r="T15" s="33"/>
-      <c r="U15" s="39"/>
-      <c r="Y15" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z15" s="53"/>
-      <c r="AA15" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB15" s="34"/>
-      <c r="AC15" s="34" t="s">
+      <c r="M18" s="86"/>
+      <c r="N18" s="87" t="s">
+        <v>66</v>
+      </c>
+      <c r="O18" s="86" t="s">
+        <v>63</v>
+      </c>
+      <c r="P18" s="86"/>
+      <c r="Q18" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="R18" s="86" t="s">
+        <v>77</v>
+      </c>
+      <c r="S18" s="88"/>
+      <c r="T18" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="U18" s="88"/>
+      <c r="Y18" s="88"/>
+      <c r="Z18" s="90"/>
+      <c r="AA18" s="82"/>
+      <c r="AB18" s="85"/>
+      <c r="AC18" s="85"/>
+      <c r="AD18" s="85"/>
+      <c r="AE18" s="86"/>
+    </row>
+    <row r="19" spans="1:32" ht="198">
+      <c r="A19" s="6">
+        <v>1001335</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C19" s="96" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" s="93">
+        <v>7894000</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="94" t="s">
+        <v>122</v>
+      </c>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="L19" s="92" t="s">
         <v>31</v>
       </c>
-      <c r="AD15" s="34" t="s">
-        <v>34</v>
-      </c>
-      <c r="AE15" s="33"/>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="10"/>
+      <c r="M19" s="92"/>
+      <c r="N19" s="87" t="s">
+        <v>32</v>
+      </c>
+      <c r="O19" s="92"/>
+      <c r="P19" s="92"/>
+      <c r="Q19" s="92"/>
+      <c r="R19" s="92"/>
+      <c r="S19" s="24"/>
+      <c r="T19" s="92"/>
+      <c r="U19" s="24"/>
+      <c r="Y19" s="24"/>
+      <c r="Z19" s="95"/>
+      <c r="AA19" s="5"/>
+      <c r="AE19" s="92"/>
+      <c r="AF19" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32">
+      <c r="D20" s="71">
+        <f>SUM(D2:D18)</f>
+        <v>67728965</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AF1" xr:uid="{D0B8D031-DB22-47ED-A6B4-22FC4BDA370C}"/>
   <mergeCells count="1">
     <mergeCell ref="Y2:Y8"/>
   </mergeCells>
   <dataValidations count="11">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q15" xr:uid="{304A6038-030B-423D-85B2-97A30E5B9E14}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2:Q19" xr:uid="{304A6038-030B-423D-85B2-97A30E5B9E14}">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P15" xr:uid="{3E1AD7A5-DE00-4CB1-B8EA-17E3E71042B0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P19" xr:uid="{3E1AD7A5-DE00-4CB1-B8EA-17E3E71042B0}">
       <formula1>"AMP, PUDC, Solar4Health, Action Opportunities, Italy UNDP Energy Partnership"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD15" xr:uid="{F42860DB-BA6C-4B30-8A9A-28104AC985C2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD19" xr:uid="{F42860DB-BA6C-4B30-8A9A-28104AC985C2}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC15 N2:N15" xr:uid="{D07DEE95-4178-413F-97C2-43B98AB92C59}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC2:AC19 N2:N19" xr:uid="{D07DEE95-4178-413F-97C2-43B98AB92C59}">
       <formula1>"Accelerating just energy transition, Close the gap on energy access, Scale up energy finance"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE15" xr:uid="{7791340A-49D5-45D0-AAB2-9DA87499FD23}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE2:AE19" xr:uid="{7791340A-49D5-45D0-AAB2-9DA87499FD23}">
       <formula1>"Tier 1, Tier 2, Tier 3"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O15" xr:uid="{63FA1942-D9FE-4EA4-8F8B-53F663803108}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O2:O19" xr:uid="{63FA1942-D9FE-4EA4-8F8B-53F663803108}">
       <formula1>"Electricity Access, Energy Efficiency, Clean Cooking, Renewable Energy, Overall"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L15" xr:uid="{23816C40-05D4-4E16-88BD-AA2F00DB37AC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L2:L19" xr:uid="{23816C40-05D4-4E16-88BD-AA2F00DB37AC}">
       <formula1>"Non-VF, VF"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M15" xr:uid="{900507B2-D87F-4BB0-A4C3-4A23A96B916D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M2:M19" xr:uid="{900507B2-D87F-4BB0-A4C3-4A23A96B916D}">
       <formula1>"Finance, Gender, Efficiency, Just, Health"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T15" xr:uid="{2991C196-C86C-408A-B119-90A37F01DB5C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2:T19" xr:uid="{2991C196-C86C-408A-B119-90A37F01DB5C}">
       <formula1>"National, Regional, City, Community"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R15" xr:uid="{4A71B761-6EA8-4568-805E-2274DE181F93}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:R19" xr:uid="{4A71B761-6EA8-4568-805E-2274DE181F93}">
       <formula1>"Electricity Access, Energy Efficiency, Renewable Energy, Infrastructure,  Transport, Digital &amp; Data, Clean Cooking, Decarbonization, Hydrogen, Off-Grid, On-Grid, Research &amp; Innovation, Grant &amp; Investment"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S15" xr:uid="{7DFBADEF-CAD9-4A79-A251-3FA16481E2BF}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S2:S19" xr:uid="{7DFBADEF-CAD9-4A79-A251-3FA16481E2BF}">
       <formula1>"Solar, Wind, Bioenergy, Hydro, Geothermal, Waste, Some Sources, Other, Unknown"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2325,8 +2828,14 @@
     <hyperlink ref="C2" r:id="rId3" xr:uid="{2FDD2CD3-4A1D-44AC-945B-AF971CA09CE4}"/>
     <hyperlink ref="C9:C12" r:id="rId4" display="https://www.undp.org/moldova/projects/addressing-impacts-energy-crisis-republic-moldova" xr:uid="{C8AAC88F-363F-4778-A2DA-825D54C305E7}"/>
     <hyperlink ref="C13" r:id="rId5" xr:uid="{CE989422-ABF1-46B8-AB73-AC4E686E8BD7}"/>
+    <hyperlink ref="C16" r:id="rId6" xr:uid="{28D6598E-8460-424B-B5C7-0C854D133F46}"/>
+    <hyperlink ref="C17" r:id="rId7" xr:uid="{477C5E6A-F5EA-4D23-B319-BFD4B1FAC357}"/>
+    <hyperlink ref="C18" r:id="rId8" xr:uid="{7806E600-B176-4A25-A9FE-F1EB0654515D}"/>
+    <hyperlink ref="C19" r:id="rId9" xr:uid="{B7B4D2A7-DFBE-49CD-B377-A4B6826D19DC}"/>
+    <hyperlink ref="C9" r:id="rId10" xr:uid="{424FC7FC-0D16-465A-A52E-F02CCB811E8C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId11"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -2334,7 +2843,7 @@
           <x14:formula1>
             <xm:f>'Beneficiary Categories'!$A$2:$A$22</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E15</xm:sqref>
+          <xm:sqref>E2:E19</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2361,459 +2870,459 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="K1" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="M1" s="22" t="s">
-        <v>97</v>
+      <c r="L1" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="M1" s="23" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="306" customHeight="1">
-      <c r="A2" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="80" t="s">
+      <c r="A2" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="82" t="s">
+      <c r="B2" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="6">
+      <c r="C2" s="109" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="7">
         <v>127500</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="111" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="104" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" s="25" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="252.75" customHeight="1">
+      <c r="A3" s="106"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="7">
+        <v>186950</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="84" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="25" t="s">
+      <c r="J3" s="111"/>
+      <c r="L3" s="100"/>
+      <c r="M3" s="25"/>
+    </row>
+    <row r="4" spans="1:13" ht="45" customHeight="1">
+      <c r="A4" s="106"/>
+      <c r="B4" s="108"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="7">
+        <v>49000</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="9">
+        <v>2020</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="111"/>
+      <c r="L4" s="100"/>
+      <c r="M4" s="25" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="94.5" customHeight="1">
+      <c r="A5" s="106"/>
+      <c r="B5" s="108"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="7">
+        <v>30000</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="9">
+        <v>2019</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="111"/>
+      <c r="L5" s="100"/>
+      <c r="M5" s="12"/>
+    </row>
+    <row r="6" spans="1:13" ht="45" customHeight="1">
+      <c r="A6" s="106"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="7">
+        <v>122000</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="L6" s="100"/>
+      <c r="M6" s="25" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="45" customHeight="1">
+      <c r="A7" s="106"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="110"/>
+      <c r="D7" s="7">
+        <v>20000</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="112" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="77" t="s">
-        <v>33</v>
-      </c>
-      <c r="M2" s="24" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="252.75" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="6">
-        <v>186950</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" s="84"/>
-      <c r="L3" s="73"/>
-      <c r="M3" s="24"/>
-    </row>
-    <row r="4" spans="1:13" ht="45" customHeight="1">
-      <c r="A4" s="79"/>
-      <c r="B4" s="81"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="6">
-        <v>49000</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="8">
-        <v>2020</v>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J4" s="84"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="24" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="94.5" customHeight="1">
-      <c r="A5" s="79"/>
-      <c r="B5" s="81"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="6">
-        <v>30000</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="L7" s="100"/>
+      <c r="M7" s="25"/>
+    </row>
+    <row r="8" spans="1:13" ht="106.5" customHeight="1">
+      <c r="A8" s="106"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="110"/>
+      <c r="D8" s="7">
+        <v>56000</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J8" s="112"/>
+      <c r="L8" s="100"/>
+      <c r="M8" s="25" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="303.75" customHeight="1">
+      <c r="A9" s="100">
+        <v>130906</v>
+      </c>
+      <c r="B9" s="101" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="102" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="14">
+        <v>649000</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="8">
-        <v>2019</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="84"/>
-      <c r="L5" s="73"/>
-      <c r="M5" s="11"/>
-    </row>
-    <row r="6" spans="1:13" ht="45" customHeight="1">
-      <c r="A6" s="79"/>
-      <c r="B6" s="81"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="6">
-        <v>122000</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J6" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="L6" s="73"/>
-      <c r="M6" s="24" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="45" customHeight="1">
-      <c r="A7" s="79"/>
-      <c r="B7" s="81"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="6">
+      <c r="F9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="15">
+        <v>2022</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" s="103" t="s">
+        <v>62</v>
+      </c>
+      <c r="M9" s="12"/>
+    </row>
+    <row r="10" spans="1:13" ht="214.5" customHeight="1">
+      <c r="A10" s="100"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="13">
+        <v>730850</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="15">
+        <v>2022</v>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J10" s="103"/>
+      <c r="M10" s="12"/>
+    </row>
+    <row r="11" spans="1:13" ht="214.5" customHeight="1">
+      <c r="A11" s="100"/>
+      <c r="B11" s="101"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="13">
+        <v>372900</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="15">
+        <v>2022</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J11" s="103"/>
+      <c r="M11" s="25" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="214.5" customHeight="1">
+      <c r="A12" s="100"/>
+      <c r="B12" s="101"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="13">
+        <v>9039075</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="15">
+        <v>2022</v>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J12" s="103"/>
+      <c r="M12" s="25" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="214.5" customHeight="1">
+      <c r="A13" s="6">
+        <v>130906</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" s="17">
+        <v>2022</v>
+      </c>
+      <c r="H13" s="4"/>
+      <c r="I13" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J13" s="103"/>
+      <c r="M13" s="12"/>
+    </row>
+    <row r="14" spans="1:13" ht="193.5" customHeight="1">
+      <c r="A14" s="6">
+        <v>1000378</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" s="7">
+        <v>2298111</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" s="4">
         <v>20000</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="85" t="s">
-        <v>28</v>
-      </c>
-      <c r="L7" s="73"/>
-      <c r="M7" s="24"/>
-    </row>
-    <row r="8" spans="1:13" ht="106.5" customHeight="1">
-      <c r="A8" s="79"/>
-      <c r="B8" s="81"/>
-      <c r="C8" s="83"/>
-      <c r="D8" s="6">
-        <v>56000</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="J8" s="85"/>
-      <c r="L8" s="73"/>
-      <c r="M8" s="24" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="303.75" customHeight="1">
-      <c r="A9" s="73">
-        <v>130906</v>
-      </c>
-      <c r="B9" s="74" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="75" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9" s="13">
-        <v>649000</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="14">
+      <c r="I14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="L14" t="s">
+        <v>31</v>
+      </c>
+      <c r="M14" s="12"/>
+    </row>
+    <row r="15" spans="1:13" ht="26.25" customHeight="1">
+      <c r="A15" s="6"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="4">
+        <v>10</v>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="18"/>
+      <c r="M15" s="12"/>
+    </row>
+    <row r="16" spans="1:13" ht="322.5" customHeight="1">
+      <c r="A16" s="6">
+        <v>133573</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="3">
         <v>2022</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="J9" s="76" t="s">
-        <v>61</v>
-      </c>
-      <c r="M9" s="11"/>
-    </row>
-    <row r="10" spans="1:13" ht="214.5" customHeight="1">
-      <c r="A10" s="73"/>
-      <c r="B10" s="74"/>
-      <c r="C10" s="75"/>
-      <c r="D10" s="12">
-        <v>730850</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="14">
-        <v>2022</v>
-      </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="J10" s="76"/>
-      <c r="M10" s="11"/>
-    </row>
-    <row r="11" spans="1:13" ht="214.5" customHeight="1">
-      <c r="A11" s="73"/>
-      <c r="B11" s="74"/>
-      <c r="C11" s="75"/>
-      <c r="D11" s="12">
-        <v>372900</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" s="14">
-        <v>2022</v>
-      </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="J11" s="76"/>
-      <c r="M11" s="24" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="214.5" customHeight="1">
-      <c r="A12" s="73"/>
-      <c r="B12" s="74"/>
-      <c r="C12" s="75"/>
-      <c r="D12" s="12">
-        <v>9039075</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G12" s="14">
-        <v>2022</v>
-      </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J12" s="76"/>
-      <c r="M12" s="24" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="214.5" customHeight="1">
-      <c r="A13" s="5">
-        <v>130906</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G13" s="16">
-        <v>2022</v>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J13" s="76"/>
-      <c r="M13" s="11"/>
-    </row>
-    <row r="14" spans="1:13" ht="193.5" customHeight="1">
-      <c r="A14" s="5">
-        <v>1000378</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D14" s="6">
-        <v>2298111</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H14" s="3">
-        <v>20000</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J14" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L14" t="s">
-        <v>30</v>
-      </c>
-      <c r="M14" s="11"/>
-    </row>
-    <row r="15" spans="1:13" ht="26.25" customHeight="1">
-      <c r="A15" s="5"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="3">
-        <v>10</v>
-      </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="17"/>
-      <c r="M15" s="11"/>
-    </row>
-    <row r="16" spans="1:13" ht="322.5" customHeight="1">
-      <c r="A16" s="5">
-        <v>133573</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G16" s="2">
-        <v>2022</v>
-      </c>
-      <c r="H16" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>111</v>
+      <c r="H16" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>141</v>
       </c>
       <c r="J16" t="s">
-        <v>95</v>
-      </c>
-      <c r="L16" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="M16" s="11"/>
+        <v>142</v>
+      </c>
+      <c r="L16" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="M16" s="12"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="10"/>
+      <c r="A18" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2872,403 +3381,403 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="166.5" customHeight="1">
-      <c r="A2" s="78" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="80" t="s">
+      <c r="A2" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="82" t="s">
+      <c r="B2" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="6">
+      <c r="C2" s="109" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="7">
         <v>127500</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="J2" s="111" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="45" customHeight="1">
+      <c r="A3" s="106"/>
+      <c r="B3" s="108"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="7">
+        <v>186950</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="J2" s="84" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="45" customHeight="1">
-      <c r="A3" s="79"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="6">
-        <v>186950</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J3" s="84"/>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="J3" s="111"/>
     </row>
     <row r="4" spans="1:10" ht="45" customHeight="1">
-      <c r="A4" s="79"/>
-      <c r="B4" s="81"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="6">
+      <c r="A4" s="106"/>
+      <c r="B4" s="108"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="7">
         <v>49000</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="8">
+      <c r="F4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="9">
         <v>2020</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="84"/>
+      <c r="H4" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="111"/>
     </row>
     <row r="5" spans="1:10" ht="94.5" customHeight="1">
-      <c r="A5" s="79"/>
-      <c r="B5" s="81"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="6">
+      <c r="A5" s="106"/>
+      <c r="B5" s="108"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="7">
         <v>30000</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="8">
+      <c r="F5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="9">
         <v>2019</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="84"/>
+      <c r="H5" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="111"/>
     </row>
     <row r="6" spans="1:10" ht="45" customHeight="1">
-      <c r="A6" s="79"/>
-      <c r="B6" s="81"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="6">
+      <c r="A6" s="106"/>
+      <c r="B6" s="108"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="7">
         <v>122000</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="45" customHeight="1">
+      <c r="A7" s="106"/>
+      <c r="B7" s="108"/>
+      <c r="C7" s="110"/>
+      <c r="D7" s="7">
+        <v>20000</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>103</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="19" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="45" customHeight="1">
-      <c r="A7" s="79"/>
-      <c r="B7" s="81"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="6">
-        <v>20000</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="85" t="s">
-        <v>28</v>
+      <c r="G7" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="112" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="61.5" customHeight="1">
-      <c r="A8" s="79"/>
-      <c r="B8" s="81"/>
-      <c r="C8" s="83"/>
-      <c r="D8" s="6">
+      <c r="A8" s="106"/>
+      <c r="B8" s="108"/>
+      <c r="C8" s="110"/>
+      <c r="D8" s="7">
         <v>56000</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="E8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="85"/>
+      <c r="F8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="112"/>
     </row>
     <row r="9" spans="1:10" ht="303.75" customHeight="1">
-      <c r="A9" s="73">
+      <c r="A9" s="100">
         <v>130906</v>
       </c>
-      <c r="B9" s="74" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="75" t="s">
+      <c r="B9" s="101" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="13">
+      <c r="C9" s="102" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="14">
         <v>649000</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="14">
+      <c r="F9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="15">
         <v>2022</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="J9" s="76" t="s">
+      <c r="I9" s="3" t="s">
         <v>61</v>
       </c>
+      <c r="J9" s="103" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="10" spans="1:10" ht="214.5" customHeight="1">
-      <c r="A10" s="73"/>
-      <c r="B10" s="74"/>
-      <c r="C10" s="75"/>
-      <c r="D10" s="12">
+      <c r="A10" s="100"/>
+      <c r="B10" s="101"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="13">
         <v>730850</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="14">
+      <c r="E10" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="15">
         <v>2022</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="76"/>
+      <c r="H10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="103"/>
     </row>
     <row r="11" spans="1:10" ht="214.5" customHeight="1">
-      <c r="A11" s="73"/>
-      <c r="B11" s="74"/>
-      <c r="C11" s="75"/>
-      <c r="D11" s="12">
+      <c r="A11" s="100"/>
+      <c r="B11" s="101"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="13">
         <v>372900</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" s="14">
+      <c r="E11" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G11" s="15">
         <v>2022</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J11" s="76"/>
+      <c r="H11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="J11" s="103"/>
     </row>
     <row r="12" spans="1:10" ht="214.5" customHeight="1">
-      <c r="A12" s="73"/>
-      <c r="B12" s="74"/>
-      <c r="C12" s="75"/>
-      <c r="D12" s="12">
+      <c r="A12" s="100"/>
+      <c r="B12" s="101"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="13">
         <v>9039075</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G12" s="14">
+      <c r="E12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" s="15">
         <v>2022</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I12" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="J12" s="76"/>
+      <c r="H12" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="I12" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="J12" s="103"/>
     </row>
     <row r="13" spans="1:10" ht="214.5" customHeight="1">
-      <c r="A13" s="5">
+      <c r="A13" s="6">
         <v>130906</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" s="21" t="s">
+      <c r="B13" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="E13" s="3" t="s">
+      <c r="C13" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="17">
         <v>2022</v>
       </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J13" s="76"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="J13" s="103"/>
     </row>
     <row r="14" spans="1:10" ht="303" customHeight="1">
-      <c r="A14" s="5">
+      <c r="A14" s="6">
         <v>1000378</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="7">
         <v>2298111</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G14" s="2" t="s">
+      <c r="E14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="4">
         <v>500</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="I14" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="J14" s="17" t="s">
+      <c r="J14" s="18" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="322.5" customHeight="1">
-      <c r="A15" s="5">
+      <c r="A15" s="6">
         <v>133573</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D15" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F15" s="9" t="s">
+      <c r="D15" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F15" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="3">
         <v>2022</v>
       </c>
-      <c r="H15" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>111</v>
+      <c r="H15" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>141</v>
       </c>
       <c r="J15" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="10"/>
+      <c r="A17" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -3314,179 +3823,179 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="54" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="45.75">
-      <c r="A2" s="86" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="56" t="s">
-        <v>128</v>
+    <row r="2" spans="1:2" ht="45">
+      <c r="A2" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="86" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="56" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="30.75">
-      <c r="A4" s="86" t="s">
-        <v>130</v>
-      </c>
-      <c r="B4" s="56" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="86" t="s">
-        <v>132</v>
-      </c>
-      <c r="B5" s="56" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="91.5">
-      <c r="A6" s="86" t="s">
-        <v>134</v>
-      </c>
-      <c r="B6" s="56" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="45.75">
-      <c r="A7" s="86" t="s">
-        <v>136</v>
-      </c>
-      <c r="B7" s="56" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="45.75">
-      <c r="A8" s="86" t="s">
-        <v>138</v>
-      </c>
-      <c r="B8" s="56" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="45.75">
-      <c r="A9" s="86" t="s">
-        <v>140</v>
-      </c>
-      <c r="B9" s="56" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="30.75">
-      <c r="A10" s="86" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="87" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="30.75">
-      <c r="A11" s="86" t="s">
-        <v>72</v>
-      </c>
-      <c r="B11" s="87" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="45.75">
-      <c r="A12" s="86" t="s">
-        <v>144</v>
-      </c>
-      <c r="B12" s="56" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30.75">
-      <c r="A13" s="86" t="s">
-        <v>53</v>
-      </c>
-      <c r="B13" s="87" t="s">
-        <v>146</v>
+      <c r="A3" s="113" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="55" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="45">
+      <c r="A4" s="113" t="s">
+        <v>161</v>
+      </c>
+      <c r="B4" s="55" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30">
+      <c r="A5" s="113" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="55" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="90">
+      <c r="A6" s="113" t="s">
+        <v>165</v>
+      </c>
+      <c r="B6" s="55" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="45">
+      <c r="A7" s="113" t="s">
+        <v>167</v>
+      </c>
+      <c r="B7" s="55" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="45">
+      <c r="A8" s="113" t="s">
+        <v>169</v>
+      </c>
+      <c r="B8" s="55" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="45">
+      <c r="A9" s="113" t="s">
+        <v>171</v>
+      </c>
+      <c r="B9" s="55" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="45">
+      <c r="A10" s="113" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="114" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="30">
+      <c r="A11" s="113" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="114" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="45">
+      <c r="A12" s="113" t="s">
+        <v>175</v>
+      </c>
+      <c r="B12" s="55" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="30">
+      <c r="A13" s="113" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="114" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="86" t="s">
-        <v>147</v>
-      </c>
-      <c r="B14" s="87" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="30.75">
-      <c r="A15" s="86" t="s">
+      <c r="A14" s="113" t="s">
+        <v>178</v>
+      </c>
+      <c r="B14" s="114" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="30">
+      <c r="A15" s="113" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="87" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30.75">
-      <c r="A16" s="86" t="s">
-        <v>150</v>
-      </c>
-      <c r="B16" s="87" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="30.75">
-      <c r="A17" s="86" t="s">
-        <v>67</v>
-      </c>
-      <c r="B17" s="56" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="30.75">
-      <c r="A18" s="86" t="s">
+      <c r="B15" s="114" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="30">
+      <c r="A16" s="113" t="s">
+        <v>181</v>
+      </c>
+      <c r="B16" s="114" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="30">
+      <c r="A17" s="113" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="55" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="30">
+      <c r="A18" s="113" t="s">
+        <v>184</v>
+      </c>
+      <c r="B18" s="114" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="75">
+      <c r="A19" s="113" t="s">
+        <v>186</v>
+      </c>
+      <c r="B19" s="114" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="30">
+      <c r="A20" s="113" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="114" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="45">
+      <c r="A21" s="113" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="115" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="30">
+      <c r="A22" s="113" t="s">
         <v>153</v>
       </c>
-      <c r="B18" s="87" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="76.5">
-      <c r="A19" s="86" t="s">
-        <v>155</v>
-      </c>
-      <c r="B19" s="87" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="30.75">
-      <c r="A20" s="86" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="87" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="45.75">
-      <c r="A21" s="86" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="88" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="30.75">
-      <c r="A22" s="86" t="s">
-        <v>122</v>
-      </c>
-      <c r="B22" s="87" t="s">
-        <v>159</v>
+      <c r="B22" s="114" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -3495,6 +4004,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010081A889D055969F449BCDADF9B8A9C0F0" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dd25160c21e587dbb66203dfb8c7aa52">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="720239d0-7d3a-4257-bb40-a2a3b1409bb2" xmlns:ns3="fb9e4d32-074f-4c04-81ef-e811753dfd59" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="05ccd5be12d50c438f9536854e894bcb" ns2:_="" ns3:_="">
     <xsd:import namespace="720239d0-7d3a-4257-bb40-a2a3b1409bb2"/>
@@ -3749,34 +4278,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="720239d0-7d3a-4257-bb40-a2a3b1409bb2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="fb9e4d32-074f-4c04-81ef-e811753dfd59" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16E1EE50-1E76-4669-A00C-97DB2E2DCEF9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DB2BDBD-B953-49D7-8E70-1D2C6591DC4D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DB2BDBD-B953-49D7-8E70-1D2C6591DC4D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1FA3D7F-F698-4E68-A900-C45E704A4D7C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1FA3D7F-F698-4E68-A900-C45E704A4D7C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16E1EE50-1E76-4669-A00C-97DB2E2DCEF9}"/>
 </file>
--- a/01_Input/00_CO Validation/Moldova Republic - Energy Projects.xlsx
+++ b/01_Input/00_CO Validation/Moldova Republic - Energy Projects.xlsx
@@ -299,7 +299,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -621,13 +621,12 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -644,10 +643,10 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -676,10 +675,10 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -705,10 +704,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -799,6 +798,56 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>CO validation update</author>
+  </authors>
+  <commentList>
+    <comment ref="K4" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L4" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K15" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L15" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K17" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L17" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="K21" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+    <comment ref="L21" authorId="0" shapeId="0">
+      <text>
+        <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1398,7 +1447,6 @@
       </c>
       <c r="W3" s="99" t="n"/>
       <c r="X3" s="39" t="n"/>
-      <c r="AB3" s="117" t="n"/>
       <c r="AC3" s="52" t="n"/>
       <c r="AD3" s="29" t="inlineStr">
         <is>
@@ -1439,12 +1487,11 @@
 Riscani and Ciocana districts</t>
         </is>
       </c>
-      <c r="K4" s="33" t="n"/>
+      <c r="K4" s="117" t="n"/>
       <c r="L4" s="118" t="n"/>
-      <c r="M4" s="119" t="inlineStr">
-        <is>
-          <t>About 5 MWh produced untill now
-[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
+      <c r="M4" s="56" t="inlineStr">
+        <is>
+          <t>About 5 MWh produced untill now</t>
         </is>
       </c>
       <c r="N4" s="61" t="n"/>
@@ -1466,7 +1513,6 @@
       </c>
       <c r="W4" s="99" t="n"/>
       <c r="X4" s="39" t="n"/>
-      <c r="AB4" s="117" t="n"/>
       <c r="AC4" s="52" t="n"/>
       <c r="AD4" s="29" t="inlineStr">
         <is>
@@ -1547,7 +1593,6 @@
       <c r="X5" s="39" t="n">
         <v>487707</v>
       </c>
-      <c r="AB5" s="117" t="n"/>
       <c r="AC5" s="52" t="n"/>
       <c r="AD5" s="29" t="inlineStr">
         <is>
@@ -1620,7 +1665,6 @@
       <c r="V6" s="39" t="n"/>
       <c r="W6" s="99" t="n"/>
       <c r="X6" s="39" t="n"/>
-      <c r="AB6" s="117" t="n"/>
       <c r="AC6" s="52" t="n"/>
       <c r="AD6" s="29" t="inlineStr">
         <is>
@@ -1681,7 +1725,6 @@
       <c r="V7" s="39" t="n"/>
       <c r="W7" s="99" t="n"/>
       <c r="X7" s="39" t="n"/>
-      <c r="AB7" s="117" t="n"/>
       <c r="AC7" s="52" t="n"/>
       <c r="AD7" s="29" t="inlineStr">
         <is>
@@ -1744,7 +1787,6 @@
       <c r="V8" s="39" t="n"/>
       <c r="W8" s="99" t="n"/>
       <c r="X8" s="39" t="n"/>
-      <c r="AB8" s="66" t="n"/>
       <c r="AC8" s="52" t="n"/>
       <c r="AD8" s="29" t="inlineStr">
         <is>
@@ -1781,9 +1823,9 @@
       <c r="D9" s="42" t="n">
         <v>649000</v>
       </c>
-      <c r="E9" s="120" t="n"/>
-      <c r="F9" s="120" t="n"/>
-      <c r="G9" s="120" t="n"/>
+      <c r="E9" s="119" t="n"/>
+      <c r="F9" s="119" t="n"/>
+      <c r="G9" s="119" t="n"/>
       <c r="H9" s="42" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -2100,13 +2142,12 @@
           <t>https://www.undp.org/moldova/projects/addressing-impacts-energy-crisis-republic-moldova</t>
         </is>
       </c>
-      <c r="D13" s="49">
-        <f>9826008+6666666</f>
-        <v/>
-      </c>
-      <c r="E13" s="121" t="n"/>
-      <c r="F13" s="121" t="n"/>
-      <c r="G13" s="121" t="n"/>
+      <c r="D13" s="49" t="n">
+        <v>16492674</v>
+      </c>
+      <c r="E13" s="120" t="n"/>
+      <c r="F13" s="120" t="n"/>
+      <c r="G13" s="120" t="n"/>
       <c r="H13" s="49" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -2298,55 +2339,51 @@
       <c r="AH14" s="99" t="n"/>
     </row>
     <row r="15" ht="322.5" customHeight="1">
-      <c r="A15" s="122" t="n"/>
-      <c r="B15" s="123" t="n"/>
+      <c r="A15" s="121" t="n"/>
+      <c r="B15" s="122" t="n"/>
       <c r="C15" s="31" t="n"/>
-      <c r="D15" s="124" t="n"/>
-      <c r="E15" s="124" t="n"/>
-      <c r="F15" s="124" t="n"/>
-      <c r="G15" s="124" t="n"/>
-      <c r="H15" s="124" t="n"/>
-      <c r="I15" s="122" t="inlineStr">
+      <c r="D15" s="123" t="n"/>
+      <c r="E15" s="123" t="n"/>
+      <c r="F15" s="123" t="n"/>
+      <c r="G15" s="123" t="n"/>
+      <c r="H15" s="123" t="n"/>
+      <c r="I15" s="121" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="J15" s="123" t="inlineStr">
+      <c r="J15" s="122" t="inlineStr">
         <is>
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K15" s="123" t="n">
+      <c r="K15" s="124" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="125" t="n"/>
-      <c r="M15" s="126" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
-      <c r="N15" s="127" t="n"/>
-      <c r="O15" s="128" t="n"/>
-      <c r="P15" s="129" t="n"/>
-      <c r="Q15" s="130" t="n"/>
-      <c r="R15" s="129" t="n"/>
-      <c r="S15" s="129" t="n"/>
-      <c r="T15" s="129" t="n"/>
-      <c r="U15" s="129" t="n"/>
-      <c r="V15" s="131" t="n"/>
-      <c r="W15" s="129" t="n"/>
-      <c r="X15" s="131" t="n"/>
-      <c r="Y15" s="132" t="n"/>
-      <c r="Z15" s="132" t="n"/>
-      <c r="AA15" s="132" t="n"/>
-      <c r="AB15" s="128" t="n"/>
+      <c r="M15" s="122" t="n"/>
+      <c r="N15" s="126" t="n"/>
+      <c r="O15" s="127" t="n"/>
+      <c r="P15" s="128" t="n"/>
+      <c r="Q15" s="129" t="n"/>
+      <c r="R15" s="128" t="n"/>
+      <c r="S15" s="128" t="n"/>
+      <c r="T15" s="128" t="n"/>
+      <c r="U15" s="128" t="n"/>
+      <c r="V15" s="130" t="n"/>
+      <c r="W15" s="128" t="n"/>
+      <c r="X15" s="130" t="n"/>
+      <c r="Y15" s="131" t="n"/>
+      <c r="Z15" s="131" t="n"/>
+      <c r="AA15" s="131" t="n"/>
+      <c r="AB15" s="127" t="n"/>
       <c r="AC15" s="52" t="n"/>
-      <c r="AD15" s="123" t="n"/>
-      <c r="AE15" s="128" t="n"/>
-      <c r="AF15" s="128" t="n"/>
-      <c r="AG15" s="128" t="n"/>
-      <c r="AH15" s="129" t="n"/>
-      <c r="AI15" s="132" t="n"/>
+      <c r="AD15" s="122" t="n"/>
+      <c r="AE15" s="127" t="n"/>
+      <c r="AF15" s="127" t="n"/>
+      <c r="AG15" s="127" t="n"/>
+      <c r="AH15" s="128" t="n"/>
+      <c r="AI15" s="131" t="n"/>
     </row>
     <row r="16" ht="322.5" customHeight="1">
       <c r="A16" s="72" t="n">
@@ -2365,9 +2402,9 @@
       <c r="D16" s="75" t="n">
         <v>4150139</v>
       </c>
-      <c r="E16" s="133" t="n"/>
-      <c r="F16" s="133" t="n"/>
-      <c r="G16" s="133" t="n"/>
+      <c r="E16" s="132" t="n"/>
+      <c r="F16" s="132" t="n"/>
+      <c r="G16" s="132" t="n"/>
       <c r="H16" s="75" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -2466,55 +2503,51 @@
       <c r="AH16" s="78" t="n"/>
     </row>
     <row r="17" ht="322.5" customHeight="1">
-      <c r="A17" s="134" t="n"/>
-      <c r="B17" s="135" t="n"/>
+      <c r="A17" s="133" t="n"/>
+      <c r="B17" s="134" t="n"/>
       <c r="C17" s="74" t="n"/>
-      <c r="D17" s="136" t="n"/>
-      <c r="E17" s="136" t="n"/>
-      <c r="F17" s="136" t="n"/>
-      <c r="G17" s="136" t="n"/>
-      <c r="H17" s="136" t="n"/>
-      <c r="I17" s="134" t="inlineStr">
+      <c r="D17" s="135" t="n"/>
+      <c r="E17" s="135" t="n"/>
+      <c r="F17" s="135" t="n"/>
+      <c r="G17" s="135" t="n"/>
+      <c r="H17" s="135" t="n"/>
+      <c r="I17" s="133" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="J17" s="135" t="inlineStr">
+      <c r="J17" s="134" t="inlineStr">
         <is>
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
       </c>
-      <c r="K17" s="135" t="n">
+      <c r="K17" s="136" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="137" t="n"/>
-      <c r="M17" s="138" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
-      <c r="N17" s="139" t="n"/>
-      <c r="O17" s="139" t="n"/>
-      <c r="P17" s="140" t="n"/>
-      <c r="Q17" s="141" t="n"/>
-      <c r="R17" s="140" t="n"/>
-      <c r="S17" s="140" t="n"/>
-      <c r="T17" s="140" t="n"/>
-      <c r="U17" s="140" t="n"/>
-      <c r="V17" s="142" t="n"/>
-      <c r="W17" s="140" t="n"/>
-      <c r="X17" s="142" t="n"/>
-      <c r="Y17" s="132" t="n"/>
-      <c r="Z17" s="132" t="n"/>
-      <c r="AA17" s="132" t="n"/>
-      <c r="AB17" s="142" t="n"/>
+      <c r="M17" s="134" t="n"/>
+      <c r="N17" s="138" t="n"/>
+      <c r="O17" s="138" t="n"/>
+      <c r="P17" s="139" t="n"/>
+      <c r="Q17" s="140" t="n"/>
+      <c r="R17" s="139" t="n"/>
+      <c r="S17" s="139" t="n"/>
+      <c r="T17" s="139" t="n"/>
+      <c r="U17" s="139" t="n"/>
+      <c r="V17" s="141" t="n"/>
+      <c r="W17" s="139" t="n"/>
+      <c r="X17" s="141" t="n"/>
+      <c r="Y17" s="131" t="n"/>
+      <c r="Z17" s="131" t="n"/>
+      <c r="AA17" s="131" t="n"/>
+      <c r="AB17" s="141" t="n"/>
       <c r="AC17" s="89" t="n"/>
-      <c r="AD17" s="135" t="n"/>
-      <c r="AE17" s="143" t="n"/>
-      <c r="AF17" s="143" t="n"/>
-      <c r="AG17" s="143" t="n"/>
-      <c r="AH17" s="140" t="n"/>
-      <c r="AI17" s="132" t="n"/>
+      <c r="AD17" s="134" t="n"/>
+      <c r="AE17" s="142" t="n"/>
+      <c r="AF17" s="142" t="n"/>
+      <c r="AG17" s="142" t="n"/>
+      <c r="AH17" s="139" t="n"/>
+      <c r="AI17" s="131" t="n"/>
     </row>
     <row r="18" ht="322.5" customHeight="1">
       <c r="A18" s="81" t="n">
@@ -2533,9 +2566,9 @@
       <c r="D18" s="91" t="n">
         <v>4268266</v>
       </c>
-      <c r="E18" s="144" t="n"/>
-      <c r="F18" s="144" t="n"/>
-      <c r="G18" s="144" t="n"/>
+      <c r="E18" s="143" t="n"/>
+      <c r="F18" s="143" t="n"/>
+      <c r="G18" s="143" t="n"/>
       <c r="H18" s="91" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -2641,9 +2674,9 @@
       <c r="D19" s="91" t="n">
         <v>20675141</v>
       </c>
-      <c r="E19" s="144" t="n"/>
-      <c r="F19" s="144" t="n"/>
-      <c r="G19" s="144" t="n"/>
+      <c r="E19" s="143" t="n"/>
+      <c r="F19" s="143" t="n"/>
+      <c r="G19" s="143" t="n"/>
       <c r="H19" s="91" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -2743,9 +2776,9 @@
       <c r="D20" s="93" t="n">
         <v>8461359</v>
       </c>
-      <c r="E20" s="145" t="n"/>
-      <c r="F20" s="145" t="n"/>
-      <c r="G20" s="145" t="n"/>
+      <c r="E20" s="144" t="n"/>
+      <c r="F20" s="144" t="n"/>
+      <c r="G20" s="144" t="n"/>
       <c r="H20" s="93" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -2837,20 +2870,20 @@
       <c r="AH20" s="86" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="146" t="n"/>
-      <c r="B21" s="147" t="n"/>
+      <c r="A21" s="145" t="n"/>
+      <c r="B21" s="146" t="n"/>
       <c r="C21" s="83" t="n"/>
       <c r="D21" s="93" t="n"/>
       <c r="E21" s="93" t="n"/>
       <c r="F21" s="93" t="n"/>
       <c r="G21" s="93" t="n"/>
       <c r="H21" s="93" t="n"/>
-      <c r="I21" s="147" t="inlineStr">
+      <c r="I21" s="146" t="inlineStr">
         <is>
           <t>Energy (MW added)</t>
         </is>
       </c>
-      <c r="J21" s="147" t="inlineStr">
+      <c r="J21" s="146" t="inlineStr">
         <is>
           <t>Installed capacity in MW for access/productive-use outputs</t>
         </is>
@@ -2859,33 +2892,29 @@
         <v>0</v>
       </c>
       <c r="L21" s="148" t="n"/>
-      <c r="M21" s="149" t="inlineStr">
-        <is>
-          <t>[AUTO-ADDED] Project reports access/productive-use beneficiary numbers but no MW value. Please add installed capacity (MW) or confirm not applicable.</t>
-        </is>
-      </c>
-      <c r="N21" s="147" t="n"/>
-      <c r="O21" s="147" t="n"/>
-      <c r="P21" s="150" t="n"/>
-      <c r="Q21" s="151" t="n"/>
-      <c r="R21" s="150" t="n"/>
-      <c r="S21" s="150" t="n"/>
-      <c r="T21" s="150" t="n"/>
-      <c r="U21" s="150" t="n"/>
-      <c r="V21" s="152" t="n"/>
-      <c r="W21" s="150" t="n"/>
-      <c r="X21" s="152" t="n"/>
-      <c r="Y21" s="132" t="n"/>
-      <c r="Z21" s="132" t="n"/>
-      <c r="AA21" s="132" t="n"/>
-      <c r="AB21" s="152" t="n"/>
+      <c r="M21" s="146" t="n"/>
+      <c r="N21" s="146" t="n"/>
+      <c r="O21" s="146" t="n"/>
+      <c r="P21" s="149" t="n"/>
+      <c r="Q21" s="150" t="n"/>
+      <c r="R21" s="149" t="n"/>
+      <c r="S21" s="149" t="n"/>
+      <c r="T21" s="149" t="n"/>
+      <c r="U21" s="149" t="n"/>
+      <c r="V21" s="151" t="n"/>
+      <c r="W21" s="149" t="n"/>
+      <c r="X21" s="151" t="n"/>
+      <c r="Y21" s="131" t="n"/>
+      <c r="Z21" s="131" t="n"/>
+      <c r="AA21" s="131" t="n"/>
+      <c r="AB21" s="151" t="n"/>
       <c r="AC21" s="90" t="n"/>
-      <c r="AD21" s="147" t="n"/>
-      <c r="AE21" s="153" t="n"/>
-      <c r="AF21" s="153" t="n"/>
-      <c r="AG21" s="153" t="n"/>
-      <c r="AH21" s="150" t="n"/>
-      <c r="AI21" s="132" t="n"/>
+      <c r="AD21" s="146" t="n"/>
+      <c r="AE21" s="152" t="n"/>
+      <c r="AF21" s="152" t="n"/>
+      <c r="AG21" s="152" t="n"/>
+      <c r="AH21" s="149" t="n"/>
+      <c r="AI21" s="131" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
@@ -2904,9 +2933,9 @@
       <c r="D22" s="93" t="n">
         <v>7894000</v>
       </c>
-      <c r="E22" s="145" t="n"/>
-      <c r="F22" s="145" t="n"/>
-      <c r="G22" s="145" t="n"/>
+      <c r="E22" s="144" t="n"/>
+      <c r="F22" s="144" t="n"/>
+      <c r="G22" s="144" t="n"/>
       <c r="H22" s="93" t="inlineStr">
         <is>
           <t>Non-VF</t>
@@ -2977,10 +3006,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AF1"/>
-  <mergeCells count="1">
-    <mergeCell ref="Y2:Y8"/>
-  </mergeCells>
-  <dataValidations count="14">
+  <dataValidations count="12">
     <dataValidation sqref="Q2:Q19" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"NDC Support, National Strategy, Legal Framework,Incentives and Support, Government Capacity-Building, Carbon Pricing and Monitoring, Financing Model, Business Model"</formula1>
     </dataValidation>
@@ -3017,12 +3043,6 @@
     <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
       <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G2001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Select a status from the dropdown list." promptTitle="Status" prompt="Choose a project status." type="list">
-      <formula1>"Pending,Approved,Active,Operationally Closed,Financially Closed,Suspended,Cancelled"</formula1>
-    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
@@ -3035,6 +3055,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -4384,12 +4405,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="154" t="inlineStr">
+      <c r="A1" s="153" t="inlineStr">
         <is>
           <t>Beneficiary Category</t>
         </is>
       </c>
-      <c r="B1" s="154" t="inlineStr">
+      <c r="B1" s="153" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
